--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0002_ses-01_WMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0002_ses-01_WMprob_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -572,7 +573,7 @@
         <v>0</v>
       </c>
       <c r="C14" s="0">
-        <v>0.001268086077682952</v>
+        <v>0</v>
       </c>
       <c r="D14" s="0">
         <v>0</v>
@@ -642,16 +643,16 @@
     </row>
     <row r="16">
       <c r="A16" s="0">
-        <v>0.0049227133996258693</v>
+        <v>0</v>
       </c>
       <c r="B16" s="0">
         <v>0</v>
       </c>
       <c r="C16" s="0">
-        <v>0.001268086077682952</v>
+        <v>0</v>
       </c>
       <c r="D16" s="0">
-        <v>0.002404250715264586</v>
+        <v>0</v>
       </c>
       <c r="E16" s="0">
         <v>0</v>
@@ -666,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="0">
-        <v>0.0019860578737264387</v>
+        <v>0</v>
       </c>
       <c r="J16" s="0">
         <v>0</v>
@@ -686,10 +687,10 @@
         <v>0</v>
       </c>
       <c r="C17" s="0">
-        <v>0.001268086077682952</v>
+        <v>0</v>
       </c>
       <c r="D17" s="0">
-        <v>0.0072127521457937566</v>
+        <v>0</v>
       </c>
       <c r="E17" s="0">
         <v>0</v>
@@ -704,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="0">
-        <v>0.0079442314949057548</v>
+        <v>0</v>
       </c>
       <c r="J17" s="0">
         <v>0</v>
@@ -718,69 +719,69 @@
     </row>
     <row r="18">
       <c r="A18" s="0">
-        <v>0.0098454267992517663</v>
+        <v>0</v>
       </c>
       <c r="B18" s="0">
-        <v>0.087719298245614197</v>
+        <v>0</v>
       </c>
       <c r="C18" s="0">
-        <v>0.0063404303884147771</v>
+        <v>0</v>
       </c>
       <c r="D18" s="0">
-        <v>0.016829755006852146</v>
+        <v>0</v>
       </c>
       <c r="E18" s="0">
         <v>0</v>
       </c>
       <c r="F18" s="0">
-        <v>0.0036386129607393729</v>
+        <v>0</v>
       </c>
       <c r="G18" s="0">
         <v>0</v>
       </c>
       <c r="H18" s="0">
-        <v>0.0056808498551383394</v>
+        <v>0</v>
       </c>
       <c r="I18" s="0">
-        <v>0.031776925979623102</v>
+        <v>0</v>
       </c>
       <c r="J18" s="0">
-        <v>0.018402649981597383</v>
+        <v>0</v>
       </c>
       <c r="K18" s="0">
         <v>0</v>
       </c>
       <c r="L18" s="0">
-        <v>0.0046651945386122686</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0">
-        <v>0.029536280397755216</v>
+        <v>0</v>
       </c>
       <c r="B19" s="0">
-        <v>0.087719298245613961</v>
+        <v>0</v>
       </c>
       <c r="C19" s="0">
-        <v>0.021557463320610183</v>
+        <v>0</v>
       </c>
       <c r="D19" s="0">
-        <v>0.033659510013704201</v>
+        <v>0</v>
       </c>
       <c r="E19" s="0">
-        <v>0.0029833825591455568</v>
+        <v>0</v>
       </c>
       <c r="F19" s="0">
-        <v>0.018193064803696816</v>
+        <v>0</v>
       </c>
       <c r="G19" s="0">
         <v>0</v>
       </c>
       <c r="H19" s="0">
-        <v>0.045446798841106584</v>
+        <v>0</v>
       </c>
       <c r="I19" s="0">
-        <v>0.081428372822783979</v>
+        <v>0</v>
       </c>
       <c r="J19" s="0">
         <v>0</v>
@@ -789,2938 +790,2938 @@
         <v>0</v>
       </c>
       <c r="L19" s="0">
-        <v>0.02021584300065311</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0">
-        <v>0.11076105149158205</v>
+        <v>0</v>
       </c>
       <c r="B20" s="0">
-        <v>0.43859649122806976</v>
+        <v>0</v>
       </c>
       <c r="C20" s="0">
-        <v>0.05833195957341579</v>
+        <v>0</v>
       </c>
       <c r="D20" s="0">
-        <v>0.10819128218690635</v>
+        <v>0</v>
       </c>
       <c r="E20" s="0">
-        <v>0.0029833825591455568</v>
+        <v>0</v>
       </c>
       <c r="F20" s="0">
-        <v>0.030928210166284584</v>
+        <v>0</v>
       </c>
       <c r="G20" s="0">
         <v>0</v>
       </c>
       <c r="H20" s="0">
-        <v>0.085212747827074858</v>
+        <v>0</v>
       </c>
       <c r="I20" s="0">
-        <v>0.17477309288792661</v>
+        <v>0</v>
       </c>
       <c r="J20" s="0">
-        <v>0.165623849834376</v>
+        <v>0</v>
       </c>
       <c r="K20" s="0">
-        <v>0.25773195876288635</v>
+        <v>0</v>
       </c>
       <c r="L20" s="0">
-        <v>0.034211426616489876</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0">
-        <v>0.23629024318204239</v>
+        <v>0</v>
       </c>
       <c r="B21" s="0">
-        <v>0.78947368421052788</v>
+        <v>0</v>
       </c>
       <c r="C21" s="0">
-        <v>0.16231501794341832</v>
+        <v>0</v>
       </c>
       <c r="D21" s="0">
-        <v>0.22119106580434247</v>
+        <v>0</v>
       </c>
       <c r="E21" s="0">
-        <v>0.014916912795727825</v>
+        <v>0</v>
       </c>
       <c r="F21" s="0">
-        <v>0.070952952734417776</v>
+        <v>0</v>
       </c>
       <c r="G21" s="0">
-        <v>0.020116676725005066</v>
+        <v>0</v>
       </c>
       <c r="H21" s="0">
-        <v>0.15338294608873515</v>
+        <v>0</v>
       </c>
       <c r="I21" s="0">
-        <v>0.38926734325038304</v>
+        <v>0</v>
       </c>
       <c r="J21" s="0">
-        <v>0.11041589988958432</v>
+        <v>0</v>
       </c>
       <c r="K21" s="0">
-        <v>0.25773195876288707</v>
+        <v>0</v>
       </c>
       <c r="L21" s="0">
-        <v>0.11351973377289855</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0">
-        <v>0.41350792556857302</v>
+        <v>0</v>
       </c>
       <c r="B22" s="0">
-        <v>1.1403508771929816</v>
+        <v>0</v>
       </c>
       <c r="C22" s="0">
-        <v>0.33984706881903115</v>
+        <v>0</v>
       </c>
       <c r="D22" s="0">
-        <v>0.49287139662924007</v>
+        <v>0</v>
       </c>
       <c r="E22" s="0">
-        <v>0.045347414899012464</v>
+        <v>0</v>
       </c>
       <c r="F22" s="0">
-        <v>0.21467816468362241</v>
+        <v>0</v>
       </c>
       <c r="G22" s="0">
-        <v>0.060350030175015036</v>
+        <v>0</v>
       </c>
       <c r="H22" s="0">
-        <v>0.47719138783161918</v>
+        <v>0</v>
       </c>
       <c r="I22" s="0">
-        <v>0.66930150344580985</v>
+        <v>0</v>
       </c>
       <c r="J22" s="0">
-        <v>0.29444239970555736</v>
+        <v>0</v>
       </c>
       <c r="K22" s="0">
-        <v>0.5154639175257727</v>
+        <v>0</v>
       </c>
       <c r="L22" s="0">
-        <v>0.23325972693061278</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0">
-        <v>0.80240228413901682</v>
+        <v>0</v>
       </c>
       <c r="B23" s="0">
-        <v>1.3157894736842093</v>
+        <v>0</v>
       </c>
       <c r="C23" s="0">
-        <v>0.65179624392903734</v>
+        <v>0.001268086077682952</v>
       </c>
       <c r="D23" s="0">
-        <v>0.99055129468900927</v>
+        <v>0</v>
       </c>
       <c r="E23" s="0">
-        <v>0.11635191980667671</v>
+        <v>0.0005966765118291113</v>
       </c>
       <c r="F23" s="0">
-        <v>0.4220791034457661</v>
+        <v>0</v>
       </c>
       <c r="G23" s="0">
-        <v>0.32186682760008017</v>
+        <v>0</v>
       </c>
       <c r="H23" s="0">
-        <v>0.76123388058853536</v>
+        <v>0</v>
       </c>
       <c r="I23" s="0">
-        <v>1.372365990744969</v>
+        <v>0</v>
       </c>
       <c r="J23" s="0">
-        <v>0.77291129922708801</v>
+        <v>0</v>
       </c>
       <c r="K23" s="0">
-        <v>1.2886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L23" s="0">
-        <v>0.51939165863216452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0">
-        <v>1.2872895540021685</v>
+        <v>0.0073840700994388248</v>
       </c>
       <c r="B24" s="0">
-        <v>3.947368421052639</v>
+        <v>0</v>
       </c>
       <c r="C24" s="0">
-        <v>1.1717115357790509</v>
+        <v>0.0012680860776829556</v>
       </c>
       <c r="D24" s="0">
-        <v>1.6974010049768022</v>
+        <v>0</v>
       </c>
       <c r="E24" s="0">
-        <v>0.25597422357468946</v>
+        <v>0.0023867060473164521</v>
       </c>
       <c r="F24" s="0">
-        <v>0.73499981806935344</v>
+        <v>0.0036386129607393729</v>
       </c>
       <c r="G24" s="0">
-        <v>0.68396700865017235</v>
+        <v>0</v>
       </c>
       <c r="H24" s="0">
-        <v>1.4940635119013832</v>
+        <v>0</v>
       </c>
       <c r="I24" s="0">
-        <v>2.001946336716256</v>
+        <v>0</v>
       </c>
       <c r="J24" s="0">
-        <v>1.5642252484357777</v>
+        <v>0</v>
       </c>
       <c r="K24" s="0">
-        <v>3.2216494845360883</v>
+        <v>0</v>
       </c>
       <c r="L24" s="0">
-        <v>0.88483189749012692</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>2.0970759082406203</v>
+        <v>0</v>
       </c>
       <c r="B25" s="0">
-        <v>4.736842105263154</v>
+        <v>0</v>
       </c>
       <c r="C25" s="0">
-        <v>1.8907163418252813</v>
+        <v>0.001268086077682952</v>
       </c>
       <c r="D25" s="0">
-        <v>2.7023778039573942</v>
+        <v>0.002404250715264586</v>
       </c>
       <c r="E25" s="0">
-        <v>0.54237894925266217</v>
+        <v>0.0023867060473164452</v>
       </c>
       <c r="F25" s="0">
-        <v>1.4226976676490908</v>
+        <v>0.018193064803696816</v>
       </c>
       <c r="G25" s="0">
-        <v>0.72420036210018035</v>
+        <v>0</v>
       </c>
       <c r="H25" s="0">
-        <v>2.2552973924899145</v>
+        <v>0</v>
       </c>
       <c r="I25" s="0">
-        <v>2.9115608428829591</v>
+        <v>0.0039721157474528774</v>
       </c>
       <c r="J25" s="0">
-        <v>2.1347073978652906</v>
+        <v>0</v>
       </c>
       <c r="K25" s="0">
-        <v>3.7371134020618522</v>
+        <v>0</v>
       </c>
       <c r="L25" s="0">
-        <v>1.5752806892047384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0">
-        <v>2.7813330707886164</v>
+        <v>0.012306783499064673</v>
       </c>
       <c r="B26" s="0">
-        <v>6.578947368421046</v>
+        <v>0</v>
       </c>
       <c r="C26" s="0">
-        <v>2.645227558046638</v>
+        <v>0.0076085164660977117</v>
       </c>
       <c r="D26" s="0">
-        <v>3.954992426610243</v>
+        <v>0</v>
       </c>
       <c r="E26" s="0">
-        <v>0.89620812076732526</v>
+        <v>0.017900295354873339</v>
       </c>
       <c r="F26" s="0">
-        <v>1.9721282247207348</v>
+        <v>0.02365098424480586</v>
       </c>
       <c r="G26" s="0">
-        <v>1.6093341380004007</v>
+        <v>0.040233353450010022</v>
       </c>
       <c r="H26" s="0">
-        <v>2.8915525762654068</v>
+        <v>0</v>
       </c>
       <c r="I26" s="0">
-        <v>3.7337888026057047</v>
+        <v>0.0079442314949057548</v>
       </c>
       <c r="J26" s="0">
-        <v>3.5149061464850906</v>
+        <v>0.03680529996319467</v>
       </c>
       <c r="K26" s="0">
-        <v>6.5721649484536027</v>
+        <v>0</v>
       </c>
       <c r="L26" s="0">
-        <v>2.2439585730724954</v>
+        <v>0.007775324231020426</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0">
-        <v>3.4237471694397925</v>
+        <v>0.027074923697942281</v>
       </c>
       <c r="B27" s="0">
-        <v>7.2807017543859587</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C27" s="0">
-        <v>3.6749134531251948</v>
+        <v>0.013948946854512471</v>
       </c>
       <c r="D27" s="0">
-        <v>4.9840117327434861</v>
+        <v>0.004808501430529172</v>
       </c>
       <c r="E27" s="0">
-        <v>1.458277394910348</v>
+        <v>0.041170679316208679</v>
       </c>
       <c r="F27" s="0">
-        <v>2.7617072372011764</v>
+        <v>0.063675726812938857</v>
       </c>
       <c r="G27" s="0">
-        <v>2.9772681553007416</v>
+        <v>0.10058338362502504</v>
       </c>
       <c r="H27" s="0">
-        <v>3.8118502527978153</v>
+        <v>0.017042549565414972</v>
       </c>
       <c r="I27" s="0">
-        <v>4.4507556950209484</v>
+        <v>0.023832694484717264</v>
       </c>
       <c r="J27" s="0">
-        <v>3.7909458962090508</v>
+        <v>0.073610599926389339</v>
       </c>
       <c r="K27" s="0">
-        <v>7.4742268041237043</v>
+        <v>0</v>
       </c>
       <c r="L27" s="0">
-        <v>3.0681429415606605</v>
+        <v>0.02954623207787762</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>3.7412621837156608</v>
+        <v>0.078763414394013909</v>
       </c>
       <c r="B28" s="0">
-        <v>7.0175438596491162</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C28" s="0">
-        <v>4.0756286536730082</v>
+        <v>0.040578754485854463</v>
       </c>
       <c r="D28" s="0">
-        <v>5.6019041665664844</v>
+        <v>0.012021253576322928</v>
       </c>
       <c r="E28" s="0">
-        <v>2.0829977027954274</v>
+        <v>0.11038515468838558</v>
       </c>
       <c r="F28" s="0">
-        <v>3.5330931848779215</v>
+        <v>0.13644798602772609</v>
       </c>
       <c r="G28" s="0">
-        <v>3.6612351639509124</v>
+        <v>0.18105009052504509</v>
       </c>
       <c r="H28" s="0">
-        <v>4.476509685848999</v>
+        <v>0.05680849855138323</v>
       </c>
       <c r="I28" s="0">
-        <v>4.7427062024587352</v>
+        <v>0.047665388969434529</v>
       </c>
       <c r="J28" s="0">
-        <v>4.5454545454545414</v>
+        <v>0.055207949944792008</v>
       </c>
       <c r="K28" s="0">
-        <v>12.886597938144318</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L28" s="0">
-        <v>3.7725873168911108</v>
+        <v>0.032656361770285788</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0">
-        <v>3.9652456433986596</v>
+        <v>0.18952446588559704</v>
       </c>
       <c r="B29" s="0">
-        <v>6.1403508771930104</v>
+        <v>0.52631578947368662</v>
       </c>
       <c r="C29" s="0">
-        <v>4.5486247606487735</v>
+        <v>0.12807669384597886</v>
       </c>
       <c r="D29" s="0">
-        <v>5.8351164859471822</v>
+        <v>0.057702017166350372</v>
       </c>
       <c r="E29" s="0">
-        <v>2.7709657209344085</v>
+        <v>0.2315104865896965</v>
       </c>
       <c r="F29" s="0">
-        <v>3.995197030891843</v>
+        <v>0.35294545719172016</v>
       </c>
       <c r="G29" s="0">
-        <v>4.425668879501127</v>
+        <v>0.74431703882518963</v>
       </c>
       <c r="H29" s="0">
-        <v>4.6128500823723444</v>
+        <v>0.19314889507470406</v>
       </c>
       <c r="I29" s="0">
-        <v>4.8896744851145186</v>
+        <v>0.12313558817103988</v>
       </c>
       <c r="J29" s="0">
-        <v>5.5391976444608284</v>
+        <v>0.20242914979757179</v>
       </c>
       <c r="K29" s="0">
-        <v>11.726804123711394</v>
+        <v>0.1288659793814439</v>
       </c>
       <c r="L29" s="0">
-        <v>4.1846795011352169</v>
+        <v>0.10729947438808249</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0">
-        <v>3.9037117259033147</v>
+        <v>0.35443536477306259</v>
       </c>
       <c r="B30" s="0">
-        <v>4.9999999999999956</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C30" s="0">
-        <v>4.5042417479298456</v>
+        <v>0.26376190415805401</v>
       </c>
       <c r="D30" s="0">
-        <v>5.5369893972543407</v>
+        <v>0.12021253576322928</v>
       </c>
       <c r="E30" s="0">
-        <v>3.3026044929741314</v>
+        <v>0.46421432620304859</v>
       </c>
       <c r="F30" s="0">
-        <v>4.2298875668595093</v>
+        <v>0.73136120510861202</v>
       </c>
       <c r="G30" s="0">
-        <v>5.1297525648762781</v>
+        <v>0.76443371555019046</v>
       </c>
       <c r="H30" s="0">
-        <v>4.3060841901948494</v>
+        <v>0.24995739362608624</v>
       </c>
       <c r="I30" s="0">
-        <v>4.8837163114933126</v>
+        <v>0.28599233381660716</v>
       </c>
       <c r="J30" s="0">
-        <v>4.6926757453073202</v>
+        <v>0.49687154950312801</v>
       </c>
       <c r="K30" s="0">
-        <v>9.020618556701022</v>
+        <v>0.90206185567010222</v>
       </c>
       <c r="L30" s="0">
-        <v>4.3277454669859692</v>
+        <v>0.21770907846857193</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>3.4926651570345539</v>
+        <v>0.67195037904893118</v>
       </c>
       <c r="B31" s="0">
-        <v>4.736842105263154</v>
+        <v>0.87719298245613953</v>
       </c>
       <c r="C31" s="0">
-        <v>4.519458780862041</v>
+        <v>0.53766849693757157</v>
       </c>
       <c r="D31" s="0">
-        <v>5.1258625249440968</v>
+        <v>0.29572283797754406</v>
       </c>
       <c r="E31" s="0">
-        <v>3.6970076672931738</v>
+        <v>0.84907067633282551</v>
       </c>
       <c r="F31" s="0">
-        <v>4.3445038751227987</v>
+        <v>1.291707601062474</v>
       </c>
       <c r="G31" s="0">
-        <v>4.9487024743512329</v>
+        <v>1.5288674311003809</v>
       </c>
       <c r="H31" s="0">
-        <v>3.8232119525080921</v>
+        <v>0.64761688348576885</v>
       </c>
       <c r="I31" s="0">
-        <v>4.4447975213997699</v>
+        <v>0.5680125518857615</v>
       </c>
       <c r="J31" s="0">
-        <v>4.1589988958409974</v>
+        <v>0.86492454913507477</v>
       </c>
       <c r="K31" s="0">
-        <v>9.9226804123711254</v>
+        <v>1.932989690721648</v>
       </c>
       <c r="L31" s="0">
-        <v>4.3557366342176431</v>
+        <v>0.50228594532391957</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0">
-        <v>3.436053952938857</v>
+        <v>1.1740671458107699</v>
       </c>
       <c r="B32" s="0">
-        <v>3.4210526315789447</v>
+        <v>1.6666666666666652</v>
       </c>
       <c r="C32" s="0">
-        <v>4.3444629021417942</v>
+        <v>1.0170050343017276</v>
       </c>
       <c r="D32" s="0">
-        <v>4.1449282331161452</v>
+        <v>0.61789243382299852</v>
       </c>
       <c r="E32" s="0">
-        <v>3.8861541215430022</v>
+        <v>1.3395387690563549</v>
       </c>
       <c r="F32" s="0">
-        <v>4.1734890659680488</v>
+        <v>1.8138485609285724</v>
       </c>
       <c r="G32" s="0">
-        <v>4.7073023536511727</v>
+        <v>2.5950512975256466</v>
       </c>
       <c r="H32" s="0">
-        <v>3.2039993182980147</v>
+        <v>1.1986593194341861</v>
       </c>
       <c r="I32" s="0">
-        <v>4.2739965442592958</v>
+        <v>1.0128895156004838</v>
       </c>
       <c r="J32" s="0">
-        <v>4.4350386455649575</v>
+        <v>1.821862348178136</v>
       </c>
       <c r="K32" s="0">
-        <v>6.5721649484536027</v>
+        <v>3.9948453608247383</v>
       </c>
       <c r="L32" s="0">
-        <v>4.0851553509781322</v>
+        <v>0.90815787018318583</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0">
-        <v>3.4828197302353026</v>
+        <v>1.8780151619572691</v>
       </c>
       <c r="B33" s="0">
-        <v>1.6666666666666652</v>
+        <v>3.9473684210526279</v>
       </c>
       <c r="C33" s="0">
-        <v>4.0211009523326409</v>
+        <v>1.6345629541333253</v>
       </c>
       <c r="D33" s="0">
-        <v>3.4212487678215049</v>
+        <v>1.1275935854590906</v>
       </c>
       <c r="E33" s="0">
-        <v>3.881380709448369</v>
+        <v>1.9332318983263208</v>
       </c>
       <c r="F33" s="0">
-        <v>3.8896772550303793</v>
+        <v>2.5543062984390326</v>
       </c>
       <c r="G33" s="0">
-        <v>3.9428686381009825</v>
+        <v>3.6008851337758969</v>
       </c>
       <c r="H33" s="0">
-        <v>2.8461057774243002</v>
+        <v>1.880361302050785</v>
       </c>
       <c r="I33" s="0">
-        <v>4.0118369049274056</v>
+        <v>1.7457448710055394</v>
       </c>
       <c r="J33" s="0">
-        <v>3.0180345969819626</v>
+        <v>2.9628266470371707</v>
       </c>
       <c r="K33" s="0">
-        <v>5.2835051546391707</v>
+        <v>4.6391752577319547</v>
       </c>
       <c r="L33" s="0">
-        <v>3.8425652349702943</v>
+        <v>1.4990825117407383</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0">
-        <v>3.4828197302353026</v>
+        <v>2.6262675987004012</v>
       </c>
       <c r="B34" s="0">
-        <v>1.5789473684210513</v>
+        <v>5.0877192982456094</v>
       </c>
       <c r="C34" s="0">
-        <v>3.9919349725459332</v>
+        <v>2.3878060842769986</v>
       </c>
       <c r="D34" s="0">
-        <v>3.058206909816553</v>
+        <v>1.8608900536147892</v>
       </c>
       <c r="E34" s="0">
-        <v>3.8587070019988632</v>
+        <v>2.6456636534502795</v>
       </c>
       <c r="F34" s="0">
-        <v>3.6859149292289746</v>
+        <v>3.3238729396354083</v>
       </c>
       <c r="G34" s="0">
-        <v>3.1985515992757962</v>
+        <v>4.5664856165761378</v>
       </c>
       <c r="H34" s="0">
-        <v>2.4086803385786495</v>
+        <v>2.669999431915012</v>
       </c>
       <c r="I34" s="0">
-        <v>3.8549383329030169</v>
+        <v>2.4825723421580483</v>
       </c>
       <c r="J34" s="0">
-        <v>2.8524107471475868</v>
+        <v>3.9013617960986347</v>
       </c>
       <c r="K34" s="0">
-        <v>2.7061855670103068</v>
+        <v>6.8298969072164884</v>
       </c>
       <c r="L34" s="0">
-        <v>3.6637327776568251</v>
+        <v>2.2657294809193522</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0">
-        <v>3.3695973220439264</v>
+        <v>3.2514522004529045</v>
       </c>
       <c r="B35" s="0">
-        <v>0.61403508771930115</v>
+        <v>7.7192982456140715</v>
       </c>
       <c r="C35" s="0">
-        <v>3.5658580504444806</v>
+        <v>3.3984706881903302</v>
       </c>
       <c r="D35" s="0">
-        <v>2.8899093597480476</v>
+        <v>3.0413771548097177</v>
       </c>
       <c r="E35" s="0">
-        <v>3.655836987976985</v>
+        <v>3.2763507264536682</v>
       </c>
       <c r="F35" s="0">
-        <v>3.4857912163883289</v>
+        <v>3.9679074336862974</v>
       </c>
       <c r="G35" s="0">
-        <v>2.8766847716757327</v>
+        <v>4.8280024140012294</v>
       </c>
       <c r="H35" s="0">
-        <v>2.4768505368403231</v>
+        <v>3.3573822643867684</v>
       </c>
       <c r="I35" s="0">
-        <v>3.6066810986872326</v>
+        <v>3.3405493436078886</v>
       </c>
       <c r="J35" s="0">
-        <v>2.0794994479205102</v>
+        <v>4.2878174457122027</v>
       </c>
       <c r="K35" s="0">
-        <v>1.8041237113402144</v>
+        <v>11.082474226804175</v>
       </c>
       <c r="L35" s="0">
-        <v>3.5735390165770076</v>
+        <v>2.9655086617112074</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0">
-        <v>3.1874569262577506</v>
+        <v>3.80771881461061</v>
       </c>
       <c r="B36" s="0">
-        <v>0.87719298245613953</v>
+        <v>6.578947368421046</v>
       </c>
       <c r="C36" s="0">
-        <v>3.3680366223259206</v>
+        <v>4.0033477472450798</v>
       </c>
       <c r="D36" s="0">
-        <v>2.9091433654701486</v>
+        <v>4.1305027288245579</v>
       </c>
       <c r="E36" s="0">
-        <v>3.5090545660670038</v>
+        <v>3.6421134282048957</v>
       </c>
       <c r="F36" s="0">
-        <v>3.3074991813120809</v>
+        <v>4.2844667612705996</v>
       </c>
       <c r="G36" s="0">
-        <v>2.4140012070006014</v>
+        <v>4.7073023536511727</v>
       </c>
       <c r="H36" s="0">
-        <v>2.3916377890132341</v>
+        <v>4.2435948417883278</v>
       </c>
       <c r="I36" s="0">
-        <v>3.2730233759011709</v>
+        <v>4.1250422037298131</v>
       </c>
       <c r="J36" s="0">
-        <v>2.2819285977180694</v>
+        <v>5.1895472948104482</v>
       </c>
       <c r="K36" s="0">
-        <v>1.0309278350515454</v>
+        <v>10.309278350515454</v>
       </c>
       <c r="L36" s="0">
-        <v>3.4226977264951919</v>
+        <v>3.7321556308898045</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>3.1160775819631752</v>
+        <v>3.7831052476124802</v>
       </c>
       <c r="B37" s="0">
-        <v>0.52631578947368374</v>
+        <v>7.5438596491228003</v>
       </c>
       <c r="C37" s="0">
-        <v>3.2653216500336013</v>
+        <v>4.4852204567646012</v>
       </c>
       <c r="D37" s="0">
-        <v>3.2625682206140425</v>
+        <v>5.1138412713677743</v>
       </c>
       <c r="E37" s="0">
-        <v>3.4696739162862822</v>
+        <v>3.8843640920075147</v>
       </c>
       <c r="F37" s="0">
-        <v>3.0346032092566286</v>
+        <v>4.2244296474184004</v>
       </c>
       <c r="G37" s="0">
-        <v>2.6956346811506715</v>
+        <v>4.5262522631261275</v>
       </c>
       <c r="H37" s="0">
-        <v>2.8574674771345769</v>
+        <v>4.5958075328069041</v>
       </c>
       <c r="I37" s="0">
-        <v>3.1598180770987638</v>
+        <v>4.7009989871104798</v>
       </c>
       <c r="J37" s="0">
-        <v>2.1347073978652906</v>
+        <v>4.9319101950680855</v>
       </c>
       <c r="K37" s="0">
-        <v>0</v>
+        <v>12.242268041237102</v>
       </c>
       <c r="L37" s="0">
-        <v>3.2158741019500483</v>
+        <v>4.1162566479022136</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>2.8182534212858106</v>
+        <v>3.9332480063010697</v>
       </c>
       <c r="B38" s="0">
-        <v>0.43859649122806976</v>
+        <v>5.1754385964912233</v>
       </c>
       <c r="C38" s="0">
-        <v>3.1156874928670133</v>
+        <v>4.7071355203591176</v>
       </c>
       <c r="D38" s="0">
-        <v>3.5174187964320884</v>
+        <v>5.7677974659197409</v>
       </c>
       <c r="E38" s="0">
-        <v>3.3043945225096181</v>
+        <v>3.8485635012977677</v>
       </c>
       <c r="F38" s="0">
-        <v>3.0819051777462403</v>
+        <v>4.2371647927809883</v>
       </c>
       <c r="G38" s="0">
-        <v>2.7761013880506913</v>
+        <v>4.3250854958760776</v>
       </c>
       <c r="H38" s="0">
-        <v>3.2721695165596745</v>
+        <v>4.3458501391808175</v>
       </c>
       <c r="I38" s="0">
-        <v>2.9473098846100352</v>
+        <v>4.8300927489026986</v>
       </c>
       <c r="J38" s="0">
-        <v>2.5027603974972377</v>
+        <v>5.2631578947368372</v>
       </c>
       <c r="K38" s="0">
-        <v>0</v>
+        <v>9.2783505154639094</v>
       </c>
       <c r="L38" s="0">
-        <v>3.0681429415606605</v>
+        <v>4.1504680745187041</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0">
-        <v>2.8256374913852489</v>
+        <v>3.6723441961208985</v>
       </c>
       <c r="B39" s="0">
-        <v>0.61403508771929771</v>
+        <v>5.1754385964912233</v>
       </c>
       <c r="C39" s="0">
-        <v>2.8925043431948136</v>
+        <v>4.5853992569015549</v>
       </c>
       <c r="D39" s="0">
-        <v>3.3683552520856845</v>
+        <v>5.7726059673502697</v>
       </c>
       <c r="E39" s="0">
-        <v>3.2107163101524478</v>
+        <v>3.8199230287299706</v>
       </c>
       <c r="F39" s="0">
-        <v>2.7471527853582192</v>
+        <v>4.0224866280973659</v>
       </c>
       <c r="G39" s="0">
-        <v>3.0175015087507515</v>
+        <v>3.1583182458257868</v>
       </c>
       <c r="H39" s="0">
-        <v>3.2892120661250899</v>
+        <v>3.8970630006248905</v>
       </c>
       <c r="I39" s="0">
-        <v>2.7765089074695615</v>
+        <v>4.7307898552163765</v>
       </c>
       <c r="J39" s="0">
-        <v>3.5517114464482855</v>
+        <v>4.1774015458225948</v>
       </c>
       <c r="K39" s="0">
-        <v>0</v>
+        <v>8.376288659793806</v>
       </c>
       <c r="L39" s="0">
-        <v>2.8986408733244149</v>
+        <v>4.3075296239853165</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0">
-        <v>2.756719503790487</v>
+        <v>3.5541990745298779</v>
       </c>
       <c r="B40" s="0">
-        <v>0.52631578947368374</v>
+        <v>3.7719298245614001</v>
       </c>
       <c r="C40" s="0">
-        <v>2.6946829150762732</v>
+        <v>4.3292458692095979</v>
       </c>
       <c r="D40" s="0">
-        <v>3.4020147620993888</v>
+        <v>5.4985213858101076</v>
       </c>
       <c r="E40" s="0">
-        <v>3.0173931203198157</v>
+        <v>3.7262448163728004</v>
       </c>
       <c r="F40" s="0">
-        <v>2.7835389149656127</v>
+        <v>3.7386748171596951</v>
       </c>
       <c r="G40" s="0">
-        <v>3.3594850130758371</v>
+        <v>2.6956346811506715</v>
       </c>
       <c r="H40" s="0">
-        <v>2.971084474237343</v>
+        <v>3.4028290632278555</v>
       </c>
       <c r="I40" s="0">
-        <v>2.6156382196977197</v>
+        <v>4.5341701257174592</v>
       </c>
       <c r="J40" s="0">
-        <v>3.1100478468899495</v>
+        <v>3.3860875966139097</v>
       </c>
       <c r="K40" s="0">
-        <v>0</v>
+        <v>6.0567010309278295</v>
       </c>
       <c r="L40" s="0">
-        <v>2.721363480857149</v>
+        <v>3.8596709482785396</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>2.6114994585015383</v>
+        <v>3.3917495323422426</v>
       </c>
       <c r="B41" s="0">
-        <v>0.87719298245614441</v>
+        <v>3.6842105263158063</v>
       </c>
       <c r="C41" s="0">
-        <v>2.6059168896384808</v>
+        <v>4.2049734335966917</v>
       </c>
       <c r="D41" s="0">
-        <v>2.9355901233380752</v>
+        <v>4.6786718919049095</v>
       </c>
       <c r="E41" s="0">
-        <v>2.9917360303111806</v>
+        <v>3.5597720695724977</v>
       </c>
       <c r="F41" s="0">
-        <v>2.5906924280464407</v>
+        <v>3.3748135210857777</v>
       </c>
       <c r="G41" s="0">
-        <v>2.7157513578756918</v>
+        <v>2.6554013277006763</v>
       </c>
       <c r="H41" s="0">
-        <v>2.6472760324944735</v>
+        <v>3.2267227177185856</v>
       </c>
       <c r="I41" s="0">
-        <v>2.5500983098647612</v>
+        <v>4.5202677206013995</v>
       </c>
       <c r="J41" s="0">
-        <v>3.0916451969083689</v>
+        <v>2.9812292970187846</v>
       </c>
       <c r="K41" s="0">
-        <v>0</v>
+        <v>4.1237113402062047</v>
       </c>
       <c r="L41" s="0">
-        <v>2.5767424501601837</v>
+        <v>3.8721114670481942</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0">
-        <v>2.4638180565127477</v>
+        <v>3.4828197302353026</v>
       </c>
       <c r="B42" s="0">
-        <v>1.0526315789473675</v>
+        <v>1.9298245614035072</v>
       </c>
       <c r="C42" s="0">
-        <v>2.5513891882980992</v>
+        <v>3.9006327749527601</v>
       </c>
       <c r="D42" s="0">
-        <v>2.531676003173609</v>
+        <v>4.1497367345466749</v>
       </c>
       <c r="E42" s="0">
-        <v>2.834213431188279</v>
+        <v>3.4714639458217693</v>
       </c>
       <c r="F42" s="0">
-        <v>2.5379325401157056</v>
+        <v>3.4093803442127833</v>
       </c>
       <c r="G42" s="0">
-        <v>2.4944679139006212</v>
+        <v>2.8766847716757167</v>
       </c>
       <c r="H42" s="0">
-        <v>2.4654888371300325</v>
+        <v>2.4484462875646176</v>
       </c>
       <c r="I42" s="0">
-        <v>2.444837242557246</v>
+        <v>4.2124287501737765</v>
       </c>
       <c r="J42" s="0">
-        <v>2.2451232977548745</v>
+        <v>2.5027603974972377</v>
       </c>
       <c r="K42" s="0">
-        <v>0</v>
+        <v>1.6752577319587614</v>
       </c>
       <c r="L42" s="0">
-        <v>2.6265045252387003</v>
+        <v>3.7166049824277643</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0">
-        <v>2.636113025499653</v>
+        <v>3.4532834498375475</v>
       </c>
       <c r="B43" s="0">
-        <v>0.96491228070175361</v>
+        <v>1.2280701754385954</v>
       </c>
       <c r="C43" s="0">
-        <v>2.4486742160057804</v>
+        <v>3.6913985721350735</v>
       </c>
       <c r="D43" s="0">
-        <v>2.1830596494602439</v>
+        <v>3.2048662034476925</v>
       </c>
       <c r="E43" s="0">
-        <v>2.7590321906978108</v>
+        <v>3.3569020555505804</v>
       </c>
       <c r="F43" s="0">
-        <v>2.3869301022450222</v>
+        <v>3.1182913073536338</v>
       </c>
       <c r="G43" s="0">
-        <v>2.2731844699255661</v>
+        <v>2.5145845906256263</v>
       </c>
       <c r="H43" s="0">
-        <v>1.9201272510367535</v>
+        <v>2.5279781855365542</v>
       </c>
       <c r="I43" s="0">
-        <v>2.1171376933923836</v>
+        <v>3.989990268316415</v>
       </c>
       <c r="J43" s="0">
-        <v>2.189915347810083</v>
+        <v>2.20831799779168</v>
       </c>
       <c r="K43" s="0">
-        <v>0</v>
+        <v>1.5463917525773183</v>
       </c>
       <c r="L43" s="0">
-        <v>2.3372624638447403</v>
+        <v>3.6497371940409886</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0">
-        <v>2.414590922516489</v>
+        <v>3.0742345180663553</v>
       </c>
       <c r="B44" s="0">
-        <v>1.9298245614035072</v>
+        <v>1.0526315789473675</v>
       </c>
       <c r="C44" s="0">
-        <v>2.1177037497305298</v>
+        <v>3.4770920250066544</v>
       </c>
       <c r="D44" s="0">
-        <v>1.7935710335873809</v>
+        <v>3.0149303969417902</v>
       </c>
       <c r="E44" s="0">
-        <v>2.6343267997255264</v>
+        <v>3.1838658671201379</v>
       </c>
       <c r="F44" s="0">
-        <v>2.2250118254921203</v>
+        <v>2.9363606593166662</v>
       </c>
       <c r="G44" s="0">
-        <v>2.0317843492255059</v>
+        <v>3.0778515389257666</v>
       </c>
       <c r="H44" s="0">
-        <v>1.7951485542237104</v>
+        <v>2.596148383798214</v>
       </c>
       <c r="I44" s="0">
-        <v>2.0515977835594112</v>
+        <v>3.6603046612778263</v>
       </c>
       <c r="J44" s="0">
-        <v>2.1347073978652906</v>
+        <v>2.5027603974972377</v>
       </c>
       <c r="K44" s="0">
-        <v>0</v>
+        <v>0.77319587628865916</v>
       </c>
       <c r="L44" s="0">
-        <v>2.3294871396137196</v>
+        <v>3.7166049824277643</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0">
-        <v>2.1659938958353826</v>
+        <v>2.9708575366742123</v>
       </c>
       <c r="B45" s="0">
-        <v>2.1929824561403488</v>
+        <v>0.78947368421052566</v>
       </c>
       <c r="C45" s="0">
-        <v>2.2305634106443124</v>
+        <v>3.2107939486932344</v>
       </c>
       <c r="D45" s="0">
-        <v>1.6180607313730662</v>
+        <v>2.8851008583175028</v>
       </c>
       <c r="E45" s="0">
-        <v>2.5937527969211467</v>
+        <v>3.0424535338166385</v>
       </c>
       <c r="F45" s="0">
-        <v>2.1376851144343756</v>
+        <v>2.9672888694829505</v>
       </c>
       <c r="G45" s="0">
-        <v>1.7702675518004409</v>
+        <v>3.4198350432508522</v>
       </c>
       <c r="H45" s="0">
-        <v>1.7610634550928805</v>
+        <v>2.6984036811907037</v>
       </c>
       <c r="I45" s="0">
-        <v>1.924490079640919</v>
+        <v>3.4438243530416446</v>
       </c>
       <c r="J45" s="0">
-        <v>1.7298490982701495</v>
+        <v>2.3371365476628614</v>
       </c>
       <c r="K45" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L45" s="0">
-        <v>2.0775666345286581</v>
+        <v>3.3542748732622116</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0">
-        <v>2.2398345968297706</v>
+        <v>2.9708575366742123</v>
       </c>
       <c r="B46" s="0">
-        <v>3.9473684210526279</v>
+        <v>0.43859649122806976</v>
       </c>
       <c r="C46" s="0">
-        <v>2.0631760483901629</v>
+        <v>3.1664109359743313</v>
       </c>
       <c r="D46" s="0">
-        <v>1.6469117399562412</v>
+        <v>3.0750366648234051</v>
       </c>
       <c r="E46" s="0">
-        <v>2.4618872878069133</v>
+        <v>2.9481786449476393</v>
       </c>
       <c r="F46" s="0">
-        <v>2.0412618709747825</v>
+        <v>2.7999126732889397</v>
       </c>
       <c r="G46" s="0">
-        <v>2.0720177026755162</v>
+        <v>3.1382015691007821</v>
       </c>
       <c r="H46" s="0">
-        <v>1.9996591490086899</v>
+        <v>2.9824461739476202</v>
       </c>
       <c r="I46" s="0">
-        <v>1.8112847808385122</v>
+        <v>3.2829536652698033</v>
       </c>
       <c r="J46" s="0">
-        <v>1.2881854987118135</v>
+        <v>2.7972027972027949</v>
       </c>
       <c r="K46" s="0">
         <v>0</v>
       </c>
       <c r="L46" s="0">
-        <v>2.0386900133735559</v>
+        <v>3.0432619040213948</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0">
-        <v>2.1093826917396967</v>
+        <v>2.9142463325785308</v>
       </c>
       <c r="B47" s="0">
-        <v>3.15789473684212</v>
+        <v>0.61403508771930115</v>
       </c>
       <c r="C47" s="0">
-        <v>1.8437971569510223</v>
+        <v>2.8950405153501957</v>
       </c>
       <c r="D47" s="0">
-        <v>1.7551030221431572</v>
+        <v>3.4140360156757304</v>
       </c>
       <c r="E47" s="0">
-        <v>2.3861093708046295</v>
+        <v>2.8282466660700032</v>
       </c>
       <c r="F47" s="0">
-        <v>1.8993559655059582</v>
+        <v>2.5543062984390468</v>
       </c>
       <c r="G47" s="0">
-        <v>1.9714343190505021</v>
+        <v>2.8163347415007172</v>
       </c>
       <c r="H47" s="0">
-        <v>2.0791910469806383</v>
+        <v>3.0222121229336052</v>
       </c>
       <c r="I47" s="0">
-        <v>1.6384977458243208</v>
+        <v>3.0684594149073647</v>
       </c>
       <c r="J47" s="0">
-        <v>1.4906146485093923</v>
+        <v>2.8708133971292003</v>
       </c>
       <c r="K47" s="0">
         <v>0</v>
       </c>
       <c r="L47" s="0">
-        <v>1.8800733990607497</v>
+        <v>2.8862003545547985</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0">
-        <v>2.1315349020380014</v>
+        <v>2.6951855862951635</v>
       </c>
       <c r="B48" s="0">
-        <v>3.5087719298245581</v>
+        <v>0.52631578947368374</v>
       </c>
       <c r="C48" s="0">
-        <v>1.8298482100964997</v>
+        <v>2.7885212848248111</v>
       </c>
       <c r="D48" s="0">
-        <v>1.7478902699973538</v>
+        <v>3.3731637535162138</v>
       </c>
       <c r="E48" s="0">
-        <v>2.247680420060262</v>
+        <v>2.8049762821086524</v>
       </c>
       <c r="F48" s="0">
-        <v>2.0012371284066495</v>
+        <v>2.5543062984390326</v>
       </c>
       <c r="G48" s="0">
-        <v>1.669684168175416</v>
+        <v>2.2731844699255661</v>
       </c>
       <c r="H48" s="0">
-        <v>1.9542123501675834</v>
+        <v>3.1187865704709399</v>
       </c>
       <c r="I48" s="0">
-        <v>1.5352227363905371</v>
+        <v>2.8182161228178164</v>
       </c>
       <c r="J48" s="0">
-        <v>1.7666543982333442</v>
+        <v>3.0364372469635601</v>
       </c>
       <c r="K48" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L48" s="0">
-        <v>1.8583024912138821</v>
+        <v>2.8146673716293944</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0">
-        <v>1.9321650093531537</v>
+        <v>2.7493354336910478</v>
       </c>
       <c r="B49" s="0">
-        <v>3.1578947368421026</v>
+        <v>0.52631578947368374</v>
       </c>
       <c r="C49" s="0">
-        <v>1.7398140985810102</v>
+        <v>2.5678743073079775</v>
       </c>
       <c r="D49" s="0">
-        <v>1.781549780011058</v>
+        <v>3.4380785228283575</v>
       </c>
       <c r="E49" s="0">
-        <v>2.2351502133118508</v>
+        <v>2.6826575971836846</v>
       </c>
       <c r="F49" s="0">
-        <v>1.8265837062911601</v>
+        <v>2.4342320707346339</v>
       </c>
       <c r="G49" s="0">
-        <v>2.5548179440756362</v>
+        <v>2.152484409575536</v>
       </c>
       <c r="H49" s="0">
-        <v>2.1359995455320098</v>
+        <v>2.9654036243822048</v>
       </c>
       <c r="I49" s="0">
-        <v>1.3743520486186955</v>
+        <v>2.667275724414607</v>
       </c>
       <c r="J49" s="0">
-        <v>1.8402649981597332</v>
+        <v>2.705189547294808</v>
       </c>
       <c r="K49" s="0">
-        <v>0.64432989690721587</v>
+        <v>0</v>
       </c>
       <c r="L49" s="0">
-        <v>1.7712188598264533</v>
+        <v>2.5471962180822918</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0">
-        <v>1.8017131042630681</v>
+        <v>2.562272324505265</v>
       </c>
       <c r="B50" s="0">
-        <v>2.4561403508771908</v>
+        <v>1.1403508771929816</v>
       </c>
       <c r="C50" s="0">
-        <v>1.5889118553367387</v>
+        <v>2.5539253604534653</v>
       </c>
       <c r="D50" s="0">
-        <v>1.6661457456783579</v>
+        <v>3.2313129613156026</v>
       </c>
       <c r="E50" s="0">
-        <v>2.1408753244428511</v>
+        <v>2.5907694143620015</v>
       </c>
       <c r="F50" s="0">
-        <v>1.6774005749008463</v>
+        <v>2.3123385365498654</v>
       </c>
       <c r="G50" s="0">
-        <v>2.2530677932005609</v>
+        <v>1.7903842285254461</v>
       </c>
       <c r="H50" s="0">
-        <v>1.9712548997329982</v>
+        <v>2.5393398852468305</v>
       </c>
       <c r="I50" s="0">
-        <v>1.3544914698814312</v>
+        <v>2.4885305157792272</v>
       </c>
       <c r="J50" s="0">
-        <v>1.6378358483621627</v>
+        <v>2.2819285977180694</v>
       </c>
       <c r="K50" s="0">
-        <v>0.77319587628865916</v>
+        <v>0</v>
       </c>
       <c r="L50" s="0">
-        <v>1.5830560134357587</v>
+        <v>2.6249494603924961</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0">
-        <v>1.7303337599684931</v>
+        <v>2.5007384070099414</v>
       </c>
       <c r="B51" s="0">
-        <v>1.6666666666666652</v>
+        <v>1.4912280701754372</v>
       </c>
       <c r="C51" s="0">
-        <v>1.614273576890398</v>
+        <v>2.5399764135989527</v>
       </c>
       <c r="D51" s="0">
-        <v>1.4473589305892804</v>
+        <v>3.1086961748371094</v>
       </c>
       <c r="E51" s="0">
-        <v>2.0495838181329975</v>
+        <v>2.4242966675616793</v>
       </c>
       <c r="F51" s="0">
-        <v>1.6300986064112346</v>
+        <v>2.1322271949932667</v>
       </c>
       <c r="G51" s="0">
-        <v>1.669684168175416</v>
+        <v>1.7702675518004409</v>
       </c>
       <c r="H51" s="0">
-        <v>1.5054252116116558</v>
+        <v>2.3405101403169892</v>
       </c>
       <c r="I51" s="0">
-        <v>1.3068260809119967</v>
+        <v>2.4408651268097934</v>
       </c>
       <c r="J51" s="0">
-        <v>1.8586676481413307</v>
+        <v>1.7850570482149415</v>
       </c>
       <c r="K51" s="0">
-        <v>0.77319587628865916</v>
+        <v>0</v>
       </c>
       <c r="L51" s="0">
-        <v>1.5286287438186159</v>
+        <v>2.3061611669206585</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0">
-        <v>1.6663384857733567</v>
+        <v>2.4835089101112509</v>
       </c>
       <c r="B52" s="0">
-        <v>0.87719298245613953</v>
+        <v>1.0526315789473675</v>
       </c>
       <c r="C52" s="0">
-        <v>1.424060665237955</v>
+        <v>2.2698740790524838</v>
       </c>
       <c r="D52" s="0">
-        <v>1.2333806169307324</v>
+        <v>2.4739739860072585</v>
       </c>
       <c r="E52" s="0">
-        <v>2.0161699334705672</v>
+        <v>2.4505504340821602</v>
       </c>
       <c r="F52" s="0">
-        <v>1.6064476221664288</v>
+        <v>2.1176727431503091</v>
       </c>
       <c r="G52" s="0">
-        <v>1.6294508147254059</v>
+        <v>1.991550995775496</v>
       </c>
       <c r="H52" s="0">
-        <v>1.7042549565414971</v>
+        <v>2.0621484974152113</v>
       </c>
       <c r="I52" s="0">
-        <v>1.181704434867231</v>
+        <v>2.2561617445532343</v>
       </c>
       <c r="J52" s="0">
-        <v>1.4906146485093841</v>
+        <v>1.9690835480309146</v>
       </c>
       <c r="K52" s="0">
-        <v>0.25773195876288635</v>
+        <v>0</v>
       </c>
       <c r="L52" s="0">
-        <v>1.5192983547413914</v>
+        <v>2.1553198768388624</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0">
-        <v>1.5383479373830842</v>
+        <v>2.3185980112237847</v>
       </c>
       <c r="B53" s="0">
-        <v>0.70175438596491169</v>
+        <v>1.8421052631578929</v>
       </c>
       <c r="C53" s="0">
-        <v>1.4088436323057596</v>
+        <v>2.1227760940412614</v>
       </c>
       <c r="D53" s="0">
-        <v>1.0242108047027134</v>
+        <v>2.0147620993917226</v>
       </c>
       <c r="E53" s="0">
-        <v>1.9278618097198588</v>
+        <v>2.3431486619529198</v>
       </c>
       <c r="F53" s="0">
-        <v>1.5518684277553383</v>
+        <v>1.9775861441618439</v>
       </c>
       <c r="G53" s="0">
-        <v>1.4484007242003607</v>
+        <v>2.0116676725005012</v>
       </c>
       <c r="H53" s="0">
-        <v>1.4827018121911024</v>
+        <v>1.6360847582798372</v>
       </c>
       <c r="I53" s="0">
-        <v>1.1102063514130791</v>
+        <v>2.1965800083414413</v>
       </c>
       <c r="J53" s="0">
-        <v>1.6562384983437601</v>
+        <v>1.6930437983069548</v>
       </c>
       <c r="K53" s="0">
-        <v>1.0309278350515454</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L53" s="0">
-        <v>1.3731222591982073</v>
+        <v>2.0900071532982905</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0">
-        <v>1.511273013685142</v>
+        <v>2.1069213350398721</v>
       </c>
       <c r="B54" s="0">
-        <v>0.35087719298245584</v>
+        <v>2.5438596491228047</v>
       </c>
       <c r="C54" s="0">
-        <v>1.3073967460911236</v>
+        <v>2.0010398305836983</v>
       </c>
       <c r="D54" s="0">
-        <v>0.85110475320366341</v>
+        <v>1.6661457456783579</v>
       </c>
       <c r="E54" s="0">
-        <v>1.8443270980637829</v>
+        <v>2.2799009516990343</v>
       </c>
       <c r="F54" s="0">
-        <v>1.4372521194920482</v>
+        <v>1.897536659025578</v>
       </c>
       <c r="G54" s="0">
-        <v>1.3880506940253456</v>
+        <v>2.1726010863005412</v>
       </c>
       <c r="H54" s="0">
-        <v>1.3747656649434743</v>
+        <v>1.8917230017610618</v>
       </c>
       <c r="I54" s="0">
-        <v>1.1022621199181735</v>
+        <v>1.9681833528629007</v>
       </c>
       <c r="J54" s="0">
-        <v>1.10415899889584</v>
+        <v>1.5274199484725786</v>
       </c>
       <c r="K54" s="0">
-        <v>0.90206185567010222</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L54" s="0">
-        <v>1.3109196653500441</v>
+        <v>1.9858178086026168</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0">
-        <v>1.3808211085950564</v>
+        <v>2.0847691247415558</v>
       </c>
       <c r="B55" s="0">
-        <v>0.26315789473684187</v>
+        <v>3.7719298245614001</v>
       </c>
       <c r="C55" s="0">
-        <v>1.1679072775459989</v>
+        <v>1.9097376329905256</v>
       </c>
       <c r="D55" s="0">
-        <v>0.71887096386411109</v>
+        <v>1.5771884692135683</v>
       </c>
       <c r="E55" s="0">
-        <v>1.7333452668635683</v>
+        <v>2.1319251767654146</v>
       </c>
       <c r="F55" s="0">
-        <v>1.3699377797183701</v>
+        <v>1.7847396572426575</v>
       </c>
       <c r="G55" s="0">
-        <v>1.3075839871253259</v>
+        <v>1.9714343190504913</v>
       </c>
       <c r="H55" s="0">
-        <v>1.2213827188547397</v>
+        <v>1.9428506504573066</v>
       </c>
       <c r="I55" s="0">
-        <v>0.88578181168199155</v>
+        <v>1.7715636233639831</v>
       </c>
       <c r="J55" s="0">
-        <v>1.2513801987486188</v>
+        <v>1.6378358483621627</v>
       </c>
       <c r="K55" s="0">
         <v>0.12886597938144317</v>
       </c>
       <c r="L55" s="0">
-        <v>1.3015892762728194</v>
+        <v>1.9935931328336376</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0">
-        <v>1.2971349808014168</v>
+        <v>2.2102983164320151</v>
       </c>
       <c r="B56" s="0">
-        <v>0.26315789473684187</v>
+        <v>3.5087719298245581</v>
       </c>
       <c r="C56" s="0">
-        <v>1.1869285687112432</v>
+        <v>1.8907163418252813</v>
       </c>
       <c r="D56" s="0">
-        <v>0.69963695814199434</v>
+        <v>1.6901882528310037</v>
       </c>
       <c r="E56" s="0">
-        <v>1.5901429040245816</v>
+        <v>2.1199916465288324</v>
       </c>
       <c r="F56" s="0">
-        <v>1.3317323436306068</v>
+        <v>1.7592693665174819</v>
       </c>
       <c r="G56" s="0">
-        <v>1.1064172198752757</v>
+        <v>1.7501508750754358</v>
       </c>
       <c r="H56" s="0">
-        <v>1.1361699710276647</v>
+        <v>1.9485315003124453</v>
       </c>
       <c r="I56" s="0">
-        <v>0.94734960576751126</v>
+        <v>1.6643164981827554</v>
       </c>
       <c r="J56" s="0">
-        <v>1.2697828487302161</v>
+        <v>1.9506808980493173</v>
       </c>
       <c r="K56" s="0">
-        <v>0.5154639175257727</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L56" s="0">
-        <v>1.2067303206543702</v>
+        <v>1.8318663888284126</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0">
-        <v>1.1371467953135883</v>
+        <v>1.9887762134488733</v>
       </c>
       <c r="B57" s="0">
-        <v>0.43859649122807465</v>
+        <v>3.4210526315789824</v>
       </c>
       <c r="C57" s="0">
-        <v>1.1083072318949123</v>
+        <v>1.8158992632420075</v>
       </c>
       <c r="D57" s="0">
-        <v>0.7549347245930883</v>
+        <v>1.7839540307263422</v>
       </c>
       <c r="E57" s="0">
-        <v>1.5119782809749849</v>
+        <v>1.973209224618893</v>
       </c>
       <c r="F57" s="0">
-        <v>1.2225739548084396</v>
+        <v>1.6846778008223438</v>
       </c>
       <c r="G57" s="0">
-        <v>1.1868839267753089</v>
+        <v>1.8507342587004818</v>
       </c>
       <c r="H57" s="0">
-        <v>1.1588933704482309</v>
+        <v>1.8405953530648371</v>
       </c>
       <c r="I57" s="0">
-        <v>0.87386546443964264</v>
+        <v>1.6206232249607917</v>
       </c>
       <c r="J57" s="0">
-        <v>1.0121457489878647</v>
+        <v>1.6378358483621809</v>
       </c>
       <c r="K57" s="0">
-        <v>0</v>
+        <v>0.38659793814433385</v>
       </c>
       <c r="L57" s="0">
-        <v>1.1103163001897294</v>
+        <v>1.7074612011321044</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0">
-        <v>1.0829969479176913</v>
+        <v>1.8460175248597011</v>
       </c>
       <c r="B58" s="0">
-        <v>0.087719298245613961</v>
+        <v>2.8947368421052606</v>
       </c>
       <c r="C58" s="0">
-        <v>1.0398305837000206</v>
+        <v>1.6713374503861309</v>
       </c>
       <c r="D58" s="0">
-        <v>0.73329646815569871</v>
+        <v>1.7983795350179099</v>
       </c>
       <c r="E58" s="0">
-        <v>1.4887078970136327</v>
+        <v>1.8675974820251184</v>
       </c>
       <c r="F58" s="0">
-        <v>1.2134774224065774</v>
+        <v>1.4609031037368543</v>
       </c>
       <c r="G58" s="0">
         <v>1.2673506336753158</v>
       </c>
       <c r="H58" s="0">
-        <v>1.1986593194341861</v>
+        <v>1.9542123501675834</v>
       </c>
       <c r="I58" s="0">
-        <v>0.76264622351095246</v>
+        <v>1.5292645627693577</v>
       </c>
       <c r="J58" s="0">
-        <v>1.0857563489142428</v>
+        <v>1.8586676481413307</v>
       </c>
       <c r="K58" s="0">
-        <v>0</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L58" s="0">
-        <v>1.0792150032656354</v>
+        <v>1.639038347899106</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0">
-        <v>1.0436152407206842</v>
+        <v>1.8189426011617589</v>
       </c>
       <c r="B59" s="0">
-        <v>0.52631578947368374</v>
+        <v>2.2807017543859631</v>
       </c>
       <c r="C59" s="0">
-        <v>0.93457943925233555</v>
+        <v>1.5178990349864936</v>
       </c>
       <c r="D59" s="0">
-        <v>0.67078594955881943</v>
+        <v>1.7430817685668247</v>
       </c>
       <c r="E59" s="0">
-        <v>1.3681792416241523</v>
+        <v>1.8491005101584159</v>
       </c>
       <c r="F59" s="0">
-        <v>1.0879452752610694</v>
+        <v>1.5118436851872052</v>
       </c>
       <c r="G59" s="0">
-        <v>1.3679340173003409</v>
+        <v>1.3075839871253259</v>
       </c>
       <c r="H59" s="0">
-        <v>1.2554678179855696</v>
+        <v>1.8746804521956468</v>
       </c>
       <c r="I59" s="0">
-        <v>0.78052074437449037</v>
+        <v>1.4518083056940268</v>
       </c>
       <c r="J59" s="0">
-        <v>1.159366948840632</v>
+        <v>1.5090172984909813</v>
       </c>
       <c r="K59" s="0">
-        <v>0.12886597938144317</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L59" s="0">
-        <v>1.0869903274966555</v>
+        <v>1.6437035424377182</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0">
-        <v>0.9451609727281669</v>
+        <v>1.5949591414787818</v>
       </c>
       <c r="B60" s="0">
-        <v>0.17543859649122792</v>
+        <v>1.7543859649122791</v>
       </c>
       <c r="C60" s="0">
-        <v>0.82679212264928481</v>
+        <v>1.50775434636503</v>
       </c>
       <c r="D60" s="0">
-        <v>0.60106267881614639</v>
+        <v>1.5170822013319536</v>
       </c>
       <c r="E60" s="0">
-        <v>1.2733076762433235</v>
+        <v>1.7745159461797773</v>
       </c>
       <c r="F60" s="0">
-        <v>1.0406433067714578</v>
+        <v>1.4699996361387027</v>
       </c>
       <c r="G60" s="0">
-        <v>1.0661838664252656</v>
+        <v>1.3478173405753358</v>
       </c>
       <c r="H60" s="0">
-        <v>1.1304891211725263</v>
+        <v>1.7099358063966355</v>
       </c>
       <c r="I60" s="0">
-        <v>0.6772457349407156</v>
+        <v>1.2690909813111944</v>
       </c>
       <c r="J60" s="0">
-        <v>0.97534044902465866</v>
+        <v>1.324990798675008</v>
       </c>
       <c r="K60" s="0">
-        <v>0.12886597938144317</v>
+        <v>1.0309278350515454</v>
       </c>
       <c r="L60" s="0">
-        <v>0.92370851864522663</v>
+        <v>1.4322147233539626</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0">
-        <v>0.82209313773752024</v>
+        <v>1.5383479373830842</v>
       </c>
       <c r="B61" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.78947368421052566</v>
       </c>
       <c r="C61" s="0">
-        <v>0.90541345946562768</v>
+        <v>1.457030903257712</v>
       </c>
       <c r="D61" s="0">
-        <v>0.43997788089341916</v>
+        <v>1.4112951698603118</v>
       </c>
       <c r="E61" s="0">
-        <v>1.2148333780840708</v>
+        <v>1.6778543512634612</v>
       </c>
       <c r="F61" s="0">
-        <v>0.96605174107630087</v>
+        <v>1.4354328130116787</v>
       </c>
       <c r="G61" s="0">
-        <v>1.0259505129752555</v>
+        <v>1.1667672500502908</v>
       </c>
       <c r="H61" s="0">
-        <v>1.0623189229108665</v>
+        <v>1.3236380162472294</v>
       </c>
       <c r="I61" s="0">
-        <v>0.66532938769835692</v>
+        <v>1.1717741454985988</v>
       </c>
       <c r="J61" s="0">
-        <v>0.86492454913507477</v>
+        <v>1.6562384983437601</v>
       </c>
       <c r="K61" s="0">
-        <v>0</v>
+        <v>0.90206185567010222</v>
       </c>
       <c r="L61" s="0">
-        <v>1.0123472148788595</v>
+        <v>1.4524305663546158</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0">
-        <v>0.84178399133602377</v>
+        <v>1.5580387909815876</v>
       </c>
       <c r="B62" s="0">
-        <v>0.70175438596491169</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C62" s="0">
-        <v>0.74817078583294172</v>
+        <v>1.2490647865177078</v>
       </c>
       <c r="D62" s="0">
-        <v>0.44719063303921291</v>
+        <v>1.178082850479647</v>
       </c>
       <c r="E62" s="0">
-        <v>1.0907246636236156</v>
+        <v>1.5513589307556894</v>
       </c>
       <c r="F62" s="0">
-        <v>0.88600225594003479</v>
+        <v>1.3335516501109765</v>
       </c>
       <c r="G62" s="0">
-        <v>0.92536712935023058</v>
+        <v>1.4282840474753558</v>
       </c>
       <c r="H62" s="0">
-        <v>1.0055104243594832</v>
+        <v>1.5111060614667942</v>
       </c>
       <c r="I62" s="0">
-        <v>0.55808226251712922</v>
+        <v>1.2293698238366655</v>
       </c>
       <c r="J62" s="0">
-        <v>0.99374309900625601</v>
+        <v>1.1777695988222294</v>
       </c>
       <c r="K62" s="0">
-        <v>0</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L62" s="0">
-        <v>0.83506982241159389</v>
+        <v>1.2984791465804111</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0">
-        <v>0.7605592202421968</v>
+        <v>1.3758983951954304</v>
       </c>
       <c r="B63" s="0">
-        <v>1.1403508771929816</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C63" s="0">
-        <v>0.77353250738660073</v>
+        <v>1.2186307206533169</v>
       </c>
       <c r="D63" s="0">
-        <v>0.34621210299810029</v>
+        <v>0.90640251965474872</v>
       </c>
       <c r="E63" s="0">
-        <v>0.99227303917181209</v>
+        <v>1.4928846325964365</v>
       </c>
       <c r="F63" s="0">
-        <v>0.92784630498853748</v>
+        <v>1.2407670196121228</v>
       </c>
       <c r="G63" s="0">
-        <v>0.98571715952524563</v>
+        <v>1.3679340173003409</v>
       </c>
       <c r="H63" s="0">
-        <v>0.93734022609782341</v>
+        <v>1.4031699142191658</v>
       </c>
       <c r="I63" s="0">
-        <v>0.56602649401203498</v>
+        <v>1.0148755734742101</v>
       </c>
       <c r="J63" s="0">
-        <v>1.0121457489878534</v>
+        <v>1.1225616488774373</v>
       </c>
       <c r="K63" s="0">
-        <v>0</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L63" s="0">
-        <v>0.81329891456473657</v>
+        <v>1.3233601841196767</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0">
-        <v>0.78271143054051329</v>
+        <v>1.2405237767057191</v>
       </c>
       <c r="B64" s="0">
-        <v>0.96491228070175361</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C64" s="0">
-        <v>0.65940476039513507</v>
+        <v>1.2097541181095362</v>
       </c>
       <c r="D64" s="0">
-        <v>0.29572283797754406</v>
+        <v>0.85591325463419243</v>
       </c>
       <c r="E64" s="0">
-        <v>0.88069453145976839</v>
+        <v>1.3544556818520828</v>
       </c>
       <c r="F64" s="0">
-        <v>0.80231415784302962</v>
+        <v>1.204380890004729</v>
       </c>
       <c r="G64" s="0">
-        <v>0.52303359485013035</v>
+        <v>1.2271172802253056</v>
       </c>
       <c r="H64" s="0">
-        <v>0.77827643015395032</v>
+        <v>1.2952337669715377</v>
       </c>
       <c r="I64" s="0">
-        <v>0.54616591527477065</v>
+        <v>1.0029592262318514</v>
       </c>
       <c r="J64" s="0">
-        <v>0.66249539933750401</v>
+        <v>0.82811924917188007</v>
       </c>
       <c r="K64" s="0">
-        <v>0</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L64" s="0">
-        <v>0.79463813641028769</v>
+        <v>1.1787391534226968</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0">
-        <v>0.65964359554986651</v>
+        <v>1.2208329231072157</v>
       </c>
       <c r="B65" s="0">
-        <v>1.5789473684210513</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C65" s="0">
-        <v>0.59726854258867035</v>
+        <v>1.0651923052536796</v>
       </c>
       <c r="D65" s="0">
-        <v>0.25725482653331067</v>
+        <v>0.79821123746784251</v>
       </c>
       <c r="E65" s="0">
-        <v>0.8281869984188065</v>
+        <v>1.2715176467078362</v>
       </c>
       <c r="F65" s="0">
-        <v>0.79321762544118113</v>
+        <v>1.1498016955936388</v>
       </c>
       <c r="G65" s="0">
-        <v>0.52303359485013035</v>
+        <v>1.0460671897002607</v>
       </c>
       <c r="H65" s="0">
-        <v>0.69306368232687543</v>
+        <v>1.1702550701584946</v>
       </c>
       <c r="I65" s="0">
-        <v>0.47665388969434525</v>
+        <v>1.0347361522114744</v>
       </c>
       <c r="J65" s="0">
-        <v>0.66249539933750401</v>
+        <v>0.95693779904306131</v>
       </c>
       <c r="K65" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L65" s="0">
-        <v>0.76353683948620588</v>
+        <v>1.1678536994992681</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0">
-        <v>0.59318696465491727</v>
+        <v>1.0903810180171301</v>
       </c>
       <c r="B66" s="0">
-        <v>1.3157894736842093</v>
+        <v>0</v>
       </c>
       <c r="C66" s="0">
-        <v>0.59600045651098743</v>
+        <v>1.001788001369532</v>
       </c>
       <c r="D66" s="0">
-        <v>0.27408458154016274</v>
+        <v>0.74050922030149235</v>
       </c>
       <c r="E66" s="0">
-        <v>0.72854202094334497</v>
+        <v>1.1879829350517606</v>
       </c>
       <c r="F66" s="0">
-        <v>0.73681912454972098</v>
+        <v>1.1024997271040269</v>
       </c>
       <c r="G66" s="0">
-        <v>0.78455039227519552</v>
+        <v>1.2271172802253056</v>
       </c>
       <c r="H66" s="0">
-        <v>0.73282963131284373</v>
+        <v>1.175935920013633</v>
       </c>
       <c r="I66" s="0">
-        <v>0.46672360032571308</v>
+        <v>0.88180969593453884</v>
       </c>
       <c r="J66" s="0">
-        <v>0.64409274935590677</v>
+        <v>1.1225616488774373</v>
       </c>
       <c r="K66" s="0">
-        <v>0</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L66" s="0">
-        <v>0.65312723540571582</v>
+        <v>1.1600783752682478</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0">
-        <v>0.58334153785566556</v>
+        <v>1.0854583046175042</v>
       </c>
       <c r="B67" s="0">
-        <v>0.96491228070175361</v>
+        <v>0</v>
       </c>
       <c r="C67" s="0">
-        <v>0.54781318555903524</v>
+        <v>0.90794963162099363</v>
       </c>
       <c r="D67" s="0">
-        <v>0.23802082081119397</v>
+        <v>0.63712643954511516</v>
       </c>
       <c r="E67" s="0">
-        <v>0.67066439929592114</v>
+        <v>1.0943047226945901</v>
       </c>
       <c r="F67" s="0">
-        <v>0.70225230142269701</v>
+        <v>1.057017065094785</v>
       </c>
       <c r="G67" s="0">
-        <v>0.70408368537517541</v>
+        <v>0.94548380607523552</v>
       </c>
       <c r="H67" s="0">
-        <v>0.64761688348576885</v>
+        <v>1.2895529171163995</v>
       </c>
       <c r="I67" s="0">
-        <v>0.44289090584099577</v>
+        <v>0.82421401759647206</v>
       </c>
       <c r="J67" s="0">
-        <v>0.55207949944792001</v>
+        <v>1.2513801987486188</v>
       </c>
       <c r="K67" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L67" s="0">
-        <v>0.65779242994432807</v>
+        <v>1.0823251329580435</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0">
-        <v>0.58334153785566556</v>
+        <v>0.91808604903022462</v>
       </c>
       <c r="B68" s="0">
-        <v>0.96491228070175361</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C68" s="0">
-        <v>0.45270672973281384</v>
+        <v>0.94726030002916517</v>
       </c>
       <c r="D68" s="0">
-        <v>0.29572283797754406</v>
+        <v>0.69242420599620058</v>
       </c>
       <c r="E68" s="0">
-        <v>0.59727318834094034</v>
+        <v>0.97914615591157173</v>
       </c>
       <c r="F68" s="0">
-        <v>0.65131171997234605</v>
+        <v>0.98424480587999774</v>
       </c>
       <c r="G68" s="0">
-        <v>0.80466706900020035</v>
+        <v>0.62361697847515529</v>
       </c>
       <c r="H68" s="0">
-        <v>0.67602113276146047</v>
+        <v>1.2270635687098779</v>
       </c>
       <c r="I68" s="0">
-        <v>0.30585291255387154</v>
+        <v>0.77257651287958462</v>
       </c>
       <c r="J68" s="0">
-        <v>0.53367684946632266</v>
+        <v>1.0305483989694506</v>
       </c>
       <c r="K68" s="0">
         <v>0</v>
       </c>
       <c r="L68" s="0">
-        <v>0.64690697602089953</v>
+        <v>0.92992877803004304</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0">
-        <v>0.49227133996259237</v>
+        <v>0.97961996652555883</v>
       </c>
       <c r="B69" s="0">
-        <v>0.43859649122807465</v>
+        <v>0.26315789473684481</v>
       </c>
       <c r="C69" s="0">
-        <v>0.41339606132464696</v>
+        <v>0.84834958596990429</v>
       </c>
       <c r="D69" s="0">
-        <v>0.25004207438751969</v>
+        <v>0.60827543096194692</v>
       </c>
       <c r="E69" s="0">
-        <v>0.53044541901608588</v>
+        <v>0.94394224171366448</v>
       </c>
       <c r="F69" s="0">
-        <v>0.55124986355201955</v>
+        <v>0.84779681985228095</v>
       </c>
       <c r="G69" s="0">
-        <v>0.54315027157514129</v>
+        <v>0.86501709917522496</v>
       </c>
       <c r="H69" s="0">
-        <v>0.63057433392036089</v>
+        <v>1.0566380730557401</v>
       </c>
       <c r="I69" s="0">
-        <v>0.31776925979623372</v>
+        <v>0.6573851562034585</v>
       </c>
       <c r="J69" s="0">
-        <v>0.57048214942952369</v>
+        <v>0.82811924917188928</v>
       </c>
       <c r="K69" s="0">
         <v>0</v>
       </c>
       <c r="L69" s="0">
-        <v>0.55671321494106873</v>
+        <v>0.90815787018319594</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0">
-        <v>0.45781234616520589</v>
+        <v>0.84424534803583662</v>
       </c>
       <c r="B70" s="0">
-        <v>0.61403508771929771</v>
+        <v>0.52631578947368374</v>
       </c>
       <c r="C70" s="0">
-        <v>0.33350663843061634</v>
+        <v>0.82171977833855292</v>
       </c>
       <c r="D70" s="0">
-        <v>0.24042507152645856</v>
+        <v>0.59384992667035264</v>
       </c>
       <c r="E70" s="0">
-        <v>0.50836838807840279</v>
+        <v>0.83534711656075578</v>
       </c>
       <c r="F70" s="0">
-        <v>0.55852708947349228</v>
+        <v>0.8405195939307929</v>
       </c>
       <c r="G70" s="0">
-        <v>0.70408368537517541</v>
+        <v>0.54315027157513529</v>
       </c>
       <c r="H70" s="0">
-        <v>0.5510424359484174</v>
+        <v>0.96006362551837676</v>
       </c>
       <c r="I70" s="0">
-        <v>0.31975531766995663</v>
+        <v>0.68916208218307418</v>
       </c>
       <c r="J70" s="0">
-        <v>0.47846889952153066</v>
+        <v>0.93853514906146396</v>
       </c>
       <c r="K70" s="0">
         <v>0</v>
       </c>
       <c r="L70" s="0">
-        <v>0.46962958355363377</v>
+        <v>0.9563648804155126</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0">
-        <v>0.41350792556857302</v>
+        <v>0.81470906763808126</v>
       </c>
       <c r="B71" s="0">
-        <v>0.43859649122806976</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C71" s="0">
-        <v>0.29926831433317669</v>
+        <v>0.79382188462952785</v>
       </c>
       <c r="D71" s="0">
-        <v>0.22599956723487105</v>
+        <v>0.51691390378188595</v>
       </c>
       <c r="E71" s="0">
-        <v>0.44154061875354234</v>
+        <v>0.7595691995584587</v>
       </c>
       <c r="F71" s="0">
-        <v>0.49667066914092306</v>
+        <v>0.76774733471600554</v>
       </c>
       <c r="G71" s="0">
-        <v>0.56326694830014024</v>
+        <v>0.54315027157513529</v>
       </c>
       <c r="H71" s="0">
-        <v>0.56808498551383235</v>
+        <v>0.8634891779810252</v>
       </c>
       <c r="I71" s="0">
-        <v>0.26811781295306919</v>
+        <v>0.55609620464340281</v>
       </c>
       <c r="J71" s="0">
-        <v>0.53367684946632266</v>
+        <v>0.66249539933750401</v>
       </c>
       <c r="K71" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L71" s="0">
-        <v>0.47118464839983787</v>
+        <v>0.79774826610269578</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0">
-        <v>0.33228315447474616</v>
+        <v>0.74086836664369338</v>
       </c>
       <c r="B72" s="0">
-        <v>0.17543859649122792</v>
+        <v>1.2280701754385954</v>
       </c>
       <c r="C72" s="0">
-        <v>0.28024702316793237</v>
+        <v>0.75577930229903934</v>
       </c>
       <c r="D72" s="0">
-        <v>0.18512730507537309</v>
+        <v>0.44959488375447748</v>
       </c>
       <c r="E72" s="0">
-        <v>0.36695605477490351</v>
+        <v>0.70765834302932595</v>
       </c>
       <c r="F72" s="0">
-        <v>0.46210384601389903</v>
+        <v>0.72408397918713319</v>
       </c>
       <c r="G72" s="0">
-        <v>0.46268356467511529</v>
+        <v>0.70408368537517541</v>
       </c>
       <c r="H72" s="0">
-        <v>0.38061694029426768</v>
+        <v>0.73282963131284373</v>
       </c>
       <c r="I72" s="0">
-        <v>0.19860578737264387</v>
+        <v>0.62163611447637524</v>
       </c>
       <c r="J72" s="0">
-        <v>0.40485829959514136</v>
+        <v>0.88332719911667212</v>
       </c>
       <c r="K72" s="0">
         <v>0</v>
       </c>
       <c r="L72" s="0">
-        <v>0.42608776785991936</v>
+        <v>0.76820203402481813</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0">
-        <v>0.35443536477306259</v>
+        <v>0.74332972334350622</v>
       </c>
       <c r="B73" s="0">
-        <v>0</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C73" s="0">
-        <v>0.19021291165244281</v>
+        <v>0.63911538315220784</v>
       </c>
       <c r="D73" s="0">
-        <v>0.10578703147164176</v>
+        <v>0.34140360156757116</v>
       </c>
       <c r="E73" s="0">
-        <v>0.32459202243503654</v>
+        <v>0.60980339508935178</v>
       </c>
       <c r="F73" s="0">
-        <v>0.47847760433722625</v>
+        <v>0.64585380053123698</v>
       </c>
       <c r="G73" s="0">
-        <v>0.38221685777509523</v>
+        <v>0.82478374572520541</v>
       </c>
       <c r="H73" s="0">
-        <v>0.40902118956995931</v>
+        <v>0.77827643015395032</v>
       </c>
       <c r="I73" s="0">
-        <v>0.18271732438283236</v>
+        <v>0.46672360032571308</v>
       </c>
       <c r="J73" s="0">
-        <v>0.5152741994847253</v>
+        <v>0.62569009937430942</v>
       </c>
       <c r="K73" s="0">
         <v>0</v>
       </c>
       <c r="L73" s="0">
-        <v>0.40742698970547042</v>
+        <v>0.77597735825583858</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0">
-        <v>0.25105838338091935</v>
+        <v>0.63749138525155003</v>
       </c>
       <c r="B74" s="0">
-        <v>0.087719298245613961</v>
+        <v>1.7543859649122791</v>
       </c>
       <c r="C74" s="0">
-        <v>0.1559745875550031</v>
+        <v>0.64165155530757367</v>
       </c>
       <c r="D74" s="0">
-        <v>0.10097853004111258</v>
+        <v>0.32457384656071908</v>
       </c>
       <c r="E74" s="0">
-        <v>0.27148781288224566</v>
+        <v>0.55848921507204819</v>
       </c>
       <c r="F74" s="0">
-        <v>0.41844049048502674</v>
+        <v>0.67678201069752153</v>
       </c>
       <c r="G74" s="0">
-        <v>0.26151679742506517</v>
+        <v>0.70408368537517541</v>
       </c>
       <c r="H74" s="0">
-        <v>0.27268079304663956</v>
+        <v>0.60217008464466237</v>
       </c>
       <c r="I74" s="0">
-        <v>0.19066155587773811</v>
+        <v>0.45480725308335446</v>
       </c>
       <c r="J74" s="0">
-        <v>0.36805299963194671</v>
+        <v>0.71770334928229607</v>
       </c>
       <c r="K74" s="0">
         <v>0</v>
       </c>
       <c r="L74" s="0">
-        <v>0.39498647093583766</v>
+        <v>0.69355892140702202</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0">
-        <v>0.2879787338781134</v>
+        <v>0.57841882445603965</v>
       </c>
       <c r="B75" s="0">
-        <v>0.26315789473684187</v>
+        <v>1.2280701754385954</v>
       </c>
       <c r="C75" s="0">
-        <v>0.097642627981587307</v>
+        <v>0.50723443107318078</v>
       </c>
       <c r="D75" s="0">
-        <v>0.10819128218690635</v>
+        <v>0.27408458154016274</v>
       </c>
       <c r="E75" s="0">
-        <v>0.27029445985858741</v>
+        <v>0.46421432620304859</v>
       </c>
       <c r="F75" s="0">
-        <v>0.37113852199541503</v>
+        <v>0.59491321908088579</v>
       </c>
       <c r="G75" s="0">
-        <v>0.22128344397505512</v>
+        <v>0.60350030175015035</v>
       </c>
       <c r="H75" s="0">
-        <v>0.27268079304663956</v>
+        <v>0.72714878145770534</v>
       </c>
       <c r="I75" s="0">
-        <v>0.13703799328712427</v>
+        <v>0.44289090584099578</v>
       </c>
       <c r="J75" s="0">
-        <v>0.25763709974236265</v>
+        <v>0.55207949944792001</v>
       </c>
       <c r="K75" s="0">
         <v>0</v>
       </c>
       <c r="L75" s="0">
-        <v>0.35144465524212326</v>
+        <v>0.61736074394302187</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0">
-        <v>0.2879787338781134</v>
+        <v>0.56365068425716203</v>
       </c>
       <c r="B76" s="0">
-        <v>0</v>
+        <v>0.87719298245613953</v>
       </c>
       <c r="C76" s="0">
-        <v>0.11032348875841681</v>
+        <v>0.46031524619891157</v>
       </c>
       <c r="D76" s="0">
-        <v>0.069723270742672983</v>
+        <v>0.2548505758180461</v>
       </c>
       <c r="E76" s="0">
-        <v>0.2500074584563976</v>
+        <v>0.42065694083952354</v>
       </c>
       <c r="F76" s="0">
-        <v>0.32565585998617302</v>
+        <v>0.55488847651275275</v>
       </c>
       <c r="G76" s="0">
-        <v>0.34198350432508523</v>
+        <v>0.54315027157513529</v>
       </c>
       <c r="H76" s="0">
-        <v>0.3124467420326078</v>
+        <v>0.67034028290632219</v>
       </c>
       <c r="I76" s="0">
-        <v>0.1390240511608507</v>
+        <v>0.4389187900935429</v>
       </c>
       <c r="J76" s="0">
-        <v>0.27603974972396</v>
+        <v>0.62569009937430942</v>
       </c>
       <c r="K76" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L76" s="0">
-        <v>0.32189842316424566</v>
+        <v>0.58159425248032792</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0">
-        <v>0.19198582258540892</v>
+        <v>0.51934626366052916</v>
       </c>
       <c r="B77" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C77" s="0">
-        <v>0.077353250738660076</v>
+        <v>0.40959180309159349</v>
       </c>
       <c r="D77" s="0">
-        <v>0.093765777895318841</v>
+        <v>0.29091433654701487</v>
       </c>
       <c r="E77" s="0">
-        <v>0.20107998448641051</v>
+        <v>0.42244697037501078</v>
       </c>
       <c r="F77" s="0">
-        <v>0.22195539060510114</v>
+        <v>0.5239602663464682</v>
       </c>
       <c r="G77" s="0">
-        <v>0.28163347415007012</v>
+        <v>0.40233353450010018</v>
       </c>
       <c r="H77" s="0">
-        <v>0.24427654377094793</v>
+        <v>0.61921263421007733</v>
       </c>
       <c r="I77" s="0">
-        <v>0.10923318305495411</v>
+        <v>0.44289090584099578</v>
       </c>
       <c r="J77" s="0">
-        <v>0.25763709974236265</v>
+        <v>0.42326094957673871</v>
       </c>
       <c r="K77" s="0">
         <v>0</v>
       </c>
       <c r="L77" s="0">
-        <v>0.25503063477747001</v>
+        <v>0.54271763132522577</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0">
-        <v>0.15752682878802782</v>
+        <v>0.48242591316333516</v>
       </c>
       <c r="B78" s="0">
-        <v>0</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C78" s="0">
-        <v>0.063404303884147598</v>
+        <v>0.35379601567354357</v>
       </c>
       <c r="D78" s="0">
-        <v>0.079340273603731332</v>
+        <v>0.28851008583175031</v>
       </c>
       <c r="E78" s="0">
-        <v>0.15394254005191071</v>
+        <v>0.33294549360064413</v>
       </c>
       <c r="F78" s="0">
-        <v>0.21831677764436178</v>
+        <v>0.48575483025870497</v>
       </c>
       <c r="G78" s="0">
-        <v>0.20116676725005009</v>
+        <v>0.22128344397505512</v>
       </c>
       <c r="H78" s="0">
-        <v>0.20451059478497965</v>
+        <v>0.68170198261659887</v>
       </c>
       <c r="I78" s="0">
-        <v>0.09334472006514262</v>
+        <v>0.32769954916486238</v>
       </c>
       <c r="J78" s="0">
-        <v>0.12881854987118133</v>
+        <v>0.4600662495399333</v>
       </c>
       <c r="K78" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L78" s="0">
-        <v>0.18816284639069433</v>
+        <v>0.55826827978726656</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0">
-        <v>0.13045190509008553</v>
+        <v>0.39135571527025664</v>
       </c>
       <c r="B79" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C79" s="0">
-        <v>0.034238324097439703</v>
+        <v>0.29292788394476188</v>
       </c>
       <c r="D79" s="0">
-        <v>0.074531772173202157</v>
+        <v>0.19955280936696063</v>
       </c>
       <c r="E79" s="0">
-        <v>0.14379903935081584</v>
+        <v>0.31683522778125811</v>
       </c>
       <c r="F79" s="0">
-        <v>0.18193064803696812</v>
+        <v>0.48029691081759596</v>
       </c>
       <c r="G79" s="0">
-        <v>0.22128344397505512</v>
+        <v>0.38221685777509523</v>
       </c>
       <c r="H79" s="0">
-        <v>0.18746804521956467</v>
+        <v>0.60785093449980066</v>
       </c>
       <c r="I79" s="0">
-        <v>0.073484141327878227</v>
+        <v>0.31776925979623016</v>
       </c>
       <c r="J79" s="0">
-        <v>0.11041589988958402</v>
+        <v>0.60728744939271206</v>
       </c>
       <c r="K79" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L79" s="0">
-        <v>0.1570615494666126</v>
+        <v>0.49140049140049097</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0">
-        <v>0.098454267992517386</v>
+        <v>0.37658757507137902</v>
       </c>
       <c r="B80" s="0">
-        <v>0</v>
+        <v>0.52631578947368374</v>
       </c>
       <c r="C80" s="0">
-        <v>0.035506410175122662</v>
+        <v>0.24600869907049267</v>
       </c>
       <c r="D80" s="0">
-        <v>0.06010626788161464</v>
+        <v>0.24282932224172316</v>
       </c>
       <c r="E80" s="0">
-        <v>0.11456189027118938</v>
+        <v>0.26253766520480898</v>
       </c>
       <c r="F80" s="0">
-        <v>0.14736382490994421</v>
+        <v>0.39297019975985126</v>
       </c>
       <c r="G80" s="0">
-        <v>0.22128344397505512</v>
+        <v>0.18105009052504509</v>
       </c>
       <c r="H80" s="0">
-        <v>0.15906379594387307</v>
+        <v>0.44878713855592761</v>
       </c>
       <c r="I80" s="0">
-        <v>0.061567794085519593</v>
+        <v>0.27606204444797494</v>
       </c>
       <c r="J80" s="0">
-        <v>0.03680529996319467</v>
+        <v>0.25763709974236265</v>
       </c>
       <c r="K80" s="0">
-        <v>0.25773195876288635</v>
+        <v>0</v>
       </c>
       <c r="L80" s="0">
-        <v>0.13840077131216358</v>
+        <v>0.48362516716947057</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0">
-        <v>0.078763414394013909</v>
+        <v>0.31997637097568149</v>
       </c>
       <c r="B81" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.52631578947368374</v>
       </c>
       <c r="C81" s="0">
-        <v>0.017753205087561331</v>
+        <v>0.2143065471284189</v>
       </c>
       <c r="D81" s="0">
-        <v>0.043276512874762536</v>
+        <v>0.18993580650590228</v>
       </c>
       <c r="E81" s="0">
-        <v>0.090098153286195803</v>
+        <v>0.21957695635311297</v>
       </c>
       <c r="F81" s="0">
-        <v>0.10551977586144153</v>
+        <v>0.37113852199541503</v>
       </c>
       <c r="G81" s="0">
-        <v>0.12070006035003007</v>
+        <v>0.28163347415007012</v>
       </c>
       <c r="H81" s="0">
-        <v>0.1192978469579048</v>
+        <v>0.44310628870078922</v>
       </c>
       <c r="I81" s="0">
-        <v>0.043693273221981653</v>
+        <v>0.24229906059462553</v>
       </c>
       <c r="J81" s="0">
-        <v>0.11041589988958402</v>
+        <v>0.57048214942951736</v>
       </c>
       <c r="K81" s="0">
         <v>0.12886597938144317</v>
       </c>
       <c r="L81" s="0">
-        <v>0.079308307156408353</v>
+        <v>0.42297763816751122</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0">
-        <v>0.056611204095698121</v>
+        <v>0.26090381018017395</v>
       </c>
       <c r="B82" s="0">
-        <v>0.17543859649122986</v>
+        <v>0</v>
       </c>
       <c r="C82" s="0">
-        <v>0.010144688621463728</v>
+        <v>0.17753205087561524</v>
       </c>
       <c r="D82" s="0">
-        <v>0.019234005722116899</v>
+        <v>0.12982953862428906</v>
       </c>
       <c r="E82" s="0">
-        <v>0.084131388167905635</v>
+        <v>0.19749992541543804</v>
       </c>
       <c r="F82" s="0">
-        <v>0.061856420332569856</v>
+        <v>0.36749990903467977</v>
       </c>
       <c r="G82" s="0">
-        <v>0.1207000603500314</v>
+        <v>0.44256688795011517</v>
       </c>
       <c r="H82" s="0">
-        <v>0.062489348406522253</v>
+        <v>0.38629779014941029</v>
       </c>
       <c r="I82" s="0">
-        <v>0.023832694484717528</v>
+        <v>0.21052213461500483</v>
       </c>
       <c r="J82" s="0">
-        <v>0.055207949944792618</v>
+        <v>0.36805299963195076</v>
       </c>
       <c r="K82" s="0">
-        <v>0.25773195876288924</v>
+        <v>0</v>
       </c>
       <c r="L82" s="0">
-        <v>0.091748825926042055</v>
+        <v>0.38254595216620924</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0">
-        <v>0.059072560795510431</v>
+        <v>0.28305602047848749</v>
       </c>
       <c r="B83" s="0">
-        <v>0.52631578947368374</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C83" s="0">
-        <v>0.01268086077682952</v>
+        <v>0.14075755462280767</v>
       </c>
       <c r="D83" s="0">
-        <v>0.036063760728968788</v>
+        <v>0.11059553290217093</v>
       </c>
       <c r="E83" s="0">
-        <v>0.059070974671082015</v>
+        <v>0.19690324890360672</v>
       </c>
       <c r="F83" s="0">
-        <v>0.047301968489611719</v>
+        <v>0.25106429429101607</v>
       </c>
       <c r="G83" s="0">
-        <v>0.060350030175015036</v>
+        <v>0.24140012070006015</v>
       </c>
       <c r="H83" s="0">
-        <v>0.079531897971936535</v>
+        <v>0.35221269101857611</v>
       </c>
       <c r="I83" s="0">
-        <v>0.033762983853349457</v>
+        <v>0.21449425036245537</v>
       </c>
       <c r="J83" s="0">
-        <v>0.03680529996319467</v>
+        <v>0.38645564961354401</v>
       </c>
       <c r="K83" s="0">
-        <v>1.1597938144329887</v>
+        <v>0</v>
       </c>
       <c r="L83" s="0">
-        <v>0.063757658694367503</v>
+        <v>0.29857245047118436</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0">
-        <v>0.046765777296445758</v>
+        <v>0.26336516687998401</v>
       </c>
       <c r="B84" s="0">
-        <v>0.17543859649122792</v>
+        <v>0</v>
       </c>
       <c r="C84" s="0">
-        <v>0.0038042582330488559</v>
+        <v>0.096374541903904348</v>
       </c>
       <c r="D84" s="0">
-        <v>0.016829755006852101</v>
+        <v>0.10578703147164176</v>
       </c>
       <c r="E84" s="0">
-        <v>0.033413884662430234</v>
+        <v>0.14678242190996138</v>
       </c>
       <c r="F84" s="0">
-        <v>0.067314339773678206</v>
+        <v>0.21831677764436178</v>
       </c>
       <c r="G84" s="0">
-        <v>0.020116676725005011</v>
+        <v>0.24140012070006015</v>
       </c>
       <c r="H84" s="0">
-        <v>0.06248934840652156</v>
+        <v>0.27268079304663956</v>
       </c>
       <c r="I84" s="0">
-        <v>0.01390240511608507</v>
+        <v>0.18271732438283236</v>
       </c>
       <c r="J84" s="0">
-        <v>0.18402649981597335</v>
+        <v>0.22083179977916803</v>
       </c>
       <c r="K84" s="0">
-        <v>1.0309278350515454</v>
+        <v>0</v>
       </c>
       <c r="L84" s="0">
-        <v>0.023325972693061282</v>
+        <v>0.29701738562498026</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0">
-        <v>0.029536280397755216</v>
+        <v>0.18460175248597011</v>
       </c>
       <c r="B85" s="0">
-        <v>0.35087719298245584</v>
+        <v>0</v>
       </c>
       <c r="C85" s="0">
-        <v>0.0088766025437806654</v>
+        <v>0.082425595049391884</v>
       </c>
       <c r="D85" s="0">
-        <v>0.004808501430529172</v>
+        <v>0.098574279325848016</v>
       </c>
       <c r="E85" s="0">
-        <v>0.029237149079626459</v>
+        <v>0.10978847817655649</v>
       </c>
       <c r="F85" s="0">
-        <v>0.02365098424480586</v>
+        <v>0.20194301932103465</v>
       </c>
       <c r="G85" s="0">
-        <v>0.040233353450010022</v>
+        <v>0.16093341380004009</v>
       </c>
       <c r="H85" s="0">
-        <v>0.051127648696244914</v>
+        <v>0.24427654377094793</v>
       </c>
       <c r="I85" s="0">
-        <v>0.011916347242358632</v>
+        <v>0.13107981966594495</v>
       </c>
       <c r="J85" s="0">
-        <v>0.092013249907986677</v>
+        <v>0.165623849834376</v>
       </c>
       <c r="K85" s="0">
-        <v>0.90206185567010222</v>
+        <v>0</v>
       </c>
       <c r="L85" s="0">
-        <v>0.021770907846857195</v>
+        <v>0.25347556993126591</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0">
-        <v>0.012306783499064673</v>
+        <v>0.17967903908634425</v>
       </c>
       <c r="B86" s="0">
-        <v>0</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C86" s="0">
-        <v>0</v>
+        <v>0.078621336816343021</v>
       </c>
       <c r="D86" s="0">
-        <v>0.0096170028610583439</v>
+        <v>0.064914769312143808</v>
       </c>
       <c r="E86" s="0">
-        <v>0.015513589307556894</v>
+        <v>0.10441838957009447</v>
       </c>
       <c r="F86" s="0">
-        <v>0.016373758323327131</v>
+        <v>0.14190590546883516</v>
       </c>
       <c r="G86" s="0">
-        <v>0.040233353450010022</v>
+        <v>0.18105009052504509</v>
       </c>
       <c r="H86" s="0">
-        <v>0.034085099130829945</v>
+        <v>0.2158722944952563</v>
       </c>
       <c r="I86" s="0">
-        <v>0.0039721157474528774</v>
+        <v>0.12710770391849208</v>
       </c>
       <c r="J86" s="0">
-        <v>0.03680529996319467</v>
+        <v>0.14722119985277868</v>
       </c>
       <c r="K86" s="0">
-        <v>2.9639175257731933</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L86" s="0">
-        <v>0.024881037539265367</v>
+        <v>0.19749323546791883</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0">
-        <v>0.0073840700994388039</v>
+        <v>0.1624495421876537</v>
       </c>
       <c r="B87" s="0">
-        <v>0.17543859649122792</v>
+        <v>0</v>
       </c>
       <c r="C87" s="0">
-        <v>0</v>
+        <v>0.043114926641220366</v>
       </c>
       <c r="D87" s="0">
-        <v>0.002404250715264586</v>
+        <v>0.091361527180054247</v>
       </c>
       <c r="E87" s="0">
-        <v>0.016110265819386006</v>
+        <v>0.076374593514126246</v>
       </c>
       <c r="F87" s="0">
-        <v>0.0090965324018484079</v>
+        <v>0.10370046938107184</v>
       </c>
       <c r="G87" s="0">
-        <v>0.020116676725005011</v>
+        <v>0.060350030175015036</v>
       </c>
       <c r="H87" s="0">
-        <v>0.028404249275691615</v>
+        <v>0.15338294608873473</v>
       </c>
       <c r="I87" s="0">
-        <v>0.0079442314949057548</v>
+        <v>0.097316835812595495</v>
       </c>
       <c r="J87" s="0">
-        <v>0.018402649981597335</v>
+        <v>0.11041589988958402</v>
       </c>
       <c r="K87" s="0">
-        <v>1.0309278350515454</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L87" s="0">
-        <v>0.013995583615836769</v>
+        <v>0.16483687369763303</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0">
-        <v>0.0073840700994388039</v>
+        <v>0.093531554592891517</v>
       </c>
       <c r="B88" s="0">
-        <v>0</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C88" s="0">
-        <v>0.001268086077682952</v>
+        <v>0.026629807631341991</v>
       </c>
       <c r="D88" s="0">
-        <v>0</v>
+        <v>0.057702017166350053</v>
       </c>
       <c r="E88" s="0">
-        <v>0.0089501476774366696</v>
+        <v>0.060861004206569355</v>
       </c>
       <c r="F88" s="0">
-        <v>0.0054579194411090446</v>
+        <v>0.072772259214787263</v>
       </c>
       <c r="G88" s="0">
         <v>0.040233353450010022</v>
       </c>
       <c r="H88" s="0">
-        <v>0</v>
+        <v>0.17610634550928805</v>
       </c>
       <c r="I88" s="0">
-        <v>0.0019860578737264387</v>
+        <v>0.08341443069651043</v>
       </c>
       <c r="J88" s="0">
-        <v>0.03680529996319467</v>
+        <v>0.12881854987118133</v>
       </c>
       <c r="K88" s="0">
-        <v>0.64432989690721587</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L88" s="0">
-        <v>0.007775324231020426</v>
+        <v>0.14462103069697993</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0">
-        <v>0</v>
+        <v>0.088608841193265647</v>
       </c>
       <c r="B89" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C89" s="0">
-        <v>0.001268086077682952</v>
+        <v>0.019021291165244279</v>
       </c>
       <c r="D89" s="0">
-        <v>0</v>
+        <v>0.091361527180054247</v>
       </c>
       <c r="E89" s="0">
-        <v>0.003580059070974668</v>
+        <v>0.039977326292550464</v>
       </c>
       <c r="F89" s="0">
-        <v>0.0018193064803696812</v>
+        <v>0.061856420332569169</v>
       </c>
       <c r="G89" s="0">
-        <v>0</v>
+        <v>0.020116676725005011</v>
       </c>
       <c r="H89" s="0">
-        <v>0.011361699710276646</v>
+        <v>0.13065954666818144</v>
       </c>
       <c r="I89" s="0">
-        <v>0</v>
+        <v>0.057595678338066718</v>
       </c>
       <c r="J89" s="0">
-        <v>0</v>
+        <v>0.092013249907986677</v>
       </c>
       <c r="K89" s="0">
-        <v>0.38659793814432958</v>
+        <v>0</v>
       </c>
       <c r="L89" s="0">
-        <v>0.0031101296924081708</v>
+        <v>0.11040960408049005</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.063995274195136301</v>
       </c>
       <c r="B90" s="0">
-        <v>0</v>
+        <v>0.35087719298245584</v>
       </c>
       <c r="C90" s="0">
-        <v>0</v>
+        <v>0.017753205087561331</v>
       </c>
       <c r="D90" s="0">
-        <v>0</v>
+        <v>0.062510518596879228</v>
       </c>
       <c r="E90" s="0">
-        <v>0.0041767355828037792</v>
+        <v>0.033413884662430234</v>
       </c>
       <c r="F90" s="0">
-        <v>0.0018193064803696812</v>
+        <v>0.036386129607393632</v>
       </c>
       <c r="G90" s="0">
-        <v>0</v>
+        <v>0.020116676725005011</v>
       </c>
       <c r="H90" s="0">
-        <v>0.011361699710276646</v>
+        <v>0.079531897971936536</v>
       </c>
       <c r="I90" s="0">
-        <v>0.0019860578737264387</v>
+        <v>0.043693273221981653</v>
       </c>
       <c r="J90" s="0">
-        <v>0</v>
+        <v>0.073610599926389339</v>
       </c>
       <c r="K90" s="0">
-        <v>0.5154639175257727</v>
+        <v>0.77319587628865916</v>
       </c>
       <c r="L90" s="0">
-        <v>0.0062202593848163417</v>
+        <v>0.088638696233632866</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.041843063896819889</v>
       </c>
       <c r="B91" s="0">
         <v>0</v>
       </c>
       <c r="C91" s="0">
-        <v>0</v>
+        <v>0.01268086077682952</v>
       </c>
       <c r="D91" s="0">
-        <v>0</v>
+        <v>0.052893515735820879</v>
       </c>
       <c r="E91" s="0">
-        <v>0.0023867060473164452</v>
+        <v>0.023867060473164455</v>
       </c>
       <c r="F91" s="0">
-        <v>0</v>
+        <v>0.040024742568132987</v>
       </c>
       <c r="G91" s="0">
-        <v>0.040233353450010022</v>
+        <v>0.10058338362502504</v>
       </c>
       <c r="H91" s="0">
-        <v>0</v>
+        <v>0.085212747827074858</v>
       </c>
       <c r="I91" s="0">
-        <v>0</v>
+        <v>0.03972115747452877</v>
       </c>
       <c r="J91" s="0">
-        <v>0</v>
+        <v>0.092013249907986677</v>
       </c>
       <c r="K91" s="0">
-        <v>0.12886597938144317</v>
+        <v>1.5463917525773183</v>
       </c>
       <c r="L91" s="0">
-        <v>0</v>
+        <v>0.046651945386122565</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0">
-        <v>0</v>
+        <v>0.041843063896819889</v>
       </c>
       <c r="B92" s="0">
-        <v>0</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C92" s="0">
-        <v>0</v>
+        <v>0.010144688621463616</v>
       </c>
       <c r="D92" s="0">
-        <v>0</v>
+        <v>0.026446757867910439</v>
       </c>
       <c r="E92" s="0">
-        <v>0.001790029535487334</v>
+        <v>0.0089501476774366696</v>
       </c>
       <c r="F92" s="0">
-        <v>0</v>
+        <v>0.020012371284066494</v>
       </c>
       <c r="G92" s="0">
-        <v>0</v>
+        <v>0.080466706900020044</v>
       </c>
       <c r="H92" s="0">
-        <v>0</v>
+        <v>0.085212747827074858</v>
       </c>
       <c r="I92" s="0">
-        <v>0</v>
+        <v>0.01588846298981151</v>
       </c>
       <c r="J92" s="0">
-        <v>0.018402649981597335</v>
+        <v>0.055207949944792008</v>
       </c>
       <c r="K92" s="0">
-        <v>0</v>
+        <v>1.1597938144329887</v>
       </c>
       <c r="L92" s="0">
-        <v>0</v>
+        <v>0.046651945386122565</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0">
-        <v>0</v>
+        <v>0.046765777296445758</v>
       </c>
       <c r="B93" s="0">
-        <v>0</v>
+        <v>0.35087719298245584</v>
       </c>
       <c r="C93" s="0">
-        <v>0</v>
+        <v>0.0038042582330488559</v>
       </c>
       <c r="D93" s="0">
-        <v>0</v>
+        <v>0.031255259298439614</v>
       </c>
       <c r="E93" s="0">
-        <v>0</v>
+        <v>0.010740177212924003</v>
       </c>
       <c r="F93" s="0">
-        <v>0</v>
+        <v>0.010915838882218089</v>
       </c>
       <c r="G93" s="0">
-        <v>0</v>
+        <v>0.020116676725005011</v>
       </c>
       <c r="H93" s="0">
-        <v>0</v>
+        <v>0.05680849855138323</v>
       </c>
       <c r="I93" s="0">
-        <v>0</v>
+        <v>0.017874520863537947</v>
       </c>
       <c r="J93" s="0">
         <v>0</v>
       </c>
       <c r="K93" s="0">
-        <v>0.12886597938144317</v>
+        <v>1.932989690721648</v>
       </c>
       <c r="L93" s="0">
-        <v>0</v>
+        <v>0.02954623207787762</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0">
-        <v>0</v>
+        <v>0.0073840700994388855</v>
       </c>
       <c r="B94" s="0">
-        <v>0</v>
+        <v>0.52631578947368962</v>
       </c>
       <c r="C94" s="0">
         <v>0</v>
       </c>
       <c r="D94" s="0">
-        <v>0</v>
+        <v>0.0072127521457938364</v>
       </c>
       <c r="E94" s="0">
-        <v>0.00059667651182911791</v>
+        <v>0.0047734120946329433</v>
       </c>
       <c r="F94" s="0">
-        <v>0</v>
+        <v>0.0054579194411091053</v>
       </c>
       <c r="G94" s="0">
         <v>0.020116676725005236</v>
       </c>
       <c r="H94" s="0">
-        <v>0</v>
+        <v>0.034085099130830319</v>
       </c>
       <c r="I94" s="0">
-        <v>0</v>
+        <v>0.011916347242358764</v>
       </c>
       <c r="J94" s="0">
-        <v>0</v>
+        <v>0.055207949944792618</v>
       </c>
       <c r="K94" s="0">
-        <v>0.12886597938144462</v>
+        <v>1.9329896907216693</v>
       </c>
       <c r="L94" s="0">
-        <v>0</v>
+        <v>0.021770907846857437</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0">
-        <v>0</v>
+        <v>0.012306783499064673</v>
       </c>
       <c r="B95" s="0">
         <v>0.087719298245613961</v>
       </c>
       <c r="C95" s="0">
-        <v>0</v>
+        <v>0.001268086077682952</v>
       </c>
       <c r="D95" s="0">
-        <v>0</v>
+        <v>0.004808501430529172</v>
       </c>
       <c r="E95" s="0">
-        <v>0</v>
+        <v>0.0011933530236582226</v>
       </c>
       <c r="F95" s="0">
-        <v>0.0018193064803696812</v>
+        <v>0.0036386129607393625</v>
       </c>
       <c r="G95" s="0">
-        <v>0</v>
+        <v>0.020116676725005011</v>
       </c>
       <c r="H95" s="0">
-        <v>0</v>
+        <v>0.034085099130829945</v>
       </c>
       <c r="I95" s="0">
-        <v>0</v>
+        <v>0.0039721157474528774</v>
       </c>
       <c r="J95" s="0">
-        <v>0</v>
+        <v>0.018402649981597335</v>
       </c>
       <c r="K95" s="0">
-        <v>0</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L95" s="0">
-        <v>0</v>
+        <v>0.0062202593848163417</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0">
-        <v>0</v>
+        <v>0.0073840700994388039</v>
       </c>
       <c r="B96" s="0">
-        <v>0</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C96" s="0">
         <v>0</v>
       </c>
       <c r="D96" s="0">
-        <v>0</v>
+        <v>0.004808501430529172</v>
       </c>
       <c r="E96" s="0">
-        <v>0</v>
+        <v>0.0011933530236582226</v>
       </c>
       <c r="F96" s="0">
-        <v>0</v>
+        <v>0.0018193064803696812</v>
       </c>
       <c r="G96" s="0">
         <v>0</v>
       </c>
       <c r="H96" s="0">
-        <v>0</v>
+        <v>0.011361699710276646</v>
       </c>
       <c r="I96" s="0">
-        <v>0</v>
+        <v>0.0059581736211793161</v>
       </c>
       <c r="J96" s="0">
         <v>0</v>
       </c>
       <c r="K96" s="0">
-        <v>0</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L96" s="0">
-        <v>0</v>
+        <v>0.0062202593848163417</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0">
-        <v>0</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B97" s="0">
         <v>0</v>
@@ -3741,16 +3742,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="0">
-        <v>0</v>
+        <v>0.005680849855138323</v>
       </c>
       <c r="I97" s="0">
-        <v>0</v>
+        <v>0.0059581736211793161</v>
       </c>
       <c r="J97" s="0">
         <v>0</v>
       </c>
       <c r="K97" s="0">
-        <v>0</v>
+        <v>0.77319587628865916</v>
       </c>
       <c r="L97" s="0">
         <v>0</v>
@@ -3761,7 +3762,7 @@
         <v>0</v>
       </c>
       <c r="B98" s="0">
-        <v>0</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C98" s="0">
         <v>0</v>
@@ -3770,16 +3771,16 @@
         <v>0</v>
       </c>
       <c r="E98" s="0">
-        <v>0</v>
+        <v>0.0005966765118291113</v>
       </c>
       <c r="F98" s="0">
-        <v>0</v>
+        <v>0.0018193064803696812</v>
       </c>
       <c r="G98" s="0">
         <v>0</v>
       </c>
       <c r="H98" s="0">
-        <v>0</v>
+        <v>0.005680849855138323</v>
       </c>
       <c r="I98" s="0">
         <v>0</v>
@@ -3788,7 +3789,7 @@
         <v>0</v>
       </c>
       <c r="K98" s="0">
-        <v>0</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L98" s="0">
         <v>0</v>
@@ -3799,7 +3800,7 @@
         <v>0</v>
       </c>
       <c r="B99" s="0">
-        <v>0</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C99" s="0">
         <v>0</v>
@@ -3840,10 +3841,10 @@
         <v>0</v>
       </c>
       <c r="C100" s="0">
-        <v>0</v>
+        <v>0.001268086077682952</v>
       </c>
       <c r="D100" s="0">
-        <v>0</v>
+        <v>0.002404250715264586</v>
       </c>
       <c r="E100" s="0">
         <v>0</v>
@@ -3861,13 +3862,13 @@
         <v>0</v>
       </c>
       <c r="J100" s="0">
-        <v>0</v>
+        <v>0.018402649981597335</v>
       </c>
       <c r="K100" s="0">
         <v>0</v>
       </c>
       <c r="L100" s="0">
-        <v>0</v>
+        <v>0.0015550648462040854</v>
       </c>
     </row>
   </sheetData>

--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0002_ses-01_WMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0002_ses-01_WMprob_pdf.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
